--- a/SpaceDebris_site_1000/2022-027B_Mozi_ji_yanzheng_xitong_attached_to_CZ-4.xlsx
+++ b/SpaceDebris_site_1000/2022-027B_Mozi_ji_yanzheng_xitong_attached_to_CZ-4.xlsx
@@ -452,7002 +452,7002 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9.720000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="B2" t="n">
-        <v>24116</v>
+        <v>38003</v>
       </c>
       <c r="C2" t="n">
-        <v>9.380000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="D2" t="n">
-        <v>22942</v>
+        <v>10721</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93.08</v>
+        <v>0.93</v>
       </c>
       <c r="B3" t="n">
-        <v>27821</v>
+        <v>35664</v>
       </c>
       <c r="C3" t="n">
-        <v>90.23</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>14656</v>
+        <v>21562</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56.07</v>
+        <v>1.44</v>
       </c>
       <c r="B4" t="n">
-        <v>23688</v>
+        <v>37933</v>
       </c>
       <c r="C4" t="n">
-        <v>58.06</v>
+        <v>1.94</v>
       </c>
       <c r="D4" t="n">
-        <v>18763</v>
+        <v>29304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>172.74</v>
+        <v>1.54</v>
       </c>
       <c r="B5" t="n">
-        <v>21027</v>
+        <v>36586</v>
       </c>
       <c r="C5" t="n">
-        <v>167.36</v>
+        <v>3.85</v>
       </c>
       <c r="D5" t="n">
-        <v>24309</v>
+        <v>26391</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>72.28</v>
+        <v>1.63</v>
       </c>
       <c r="B6" t="n">
-        <v>24563</v>
+        <v>36384</v>
       </c>
       <c r="C6" t="n">
-        <v>70.91</v>
+        <v>6.94</v>
       </c>
       <c r="D6" t="n">
-        <v>25332</v>
+        <v>17443</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105.14</v>
+        <v>1.82</v>
       </c>
       <c r="B7" t="n">
-        <v>46293</v>
+        <v>37530</v>
       </c>
       <c r="C7" t="n">
-        <v>106.32</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>20111</v>
+        <v>17980</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110.27</v>
+        <v>1.99</v>
       </c>
       <c r="B8" t="n">
-        <v>31509</v>
+        <v>35932</v>
       </c>
       <c r="C8" t="n">
-        <v>114.71</v>
+        <v>1.12</v>
       </c>
       <c r="D8" t="n">
-        <v>23833</v>
+        <v>10018</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98.06999999999999</v>
+        <v>2.37</v>
       </c>
       <c r="B9" t="n">
-        <v>44513</v>
+        <v>35237</v>
       </c>
       <c r="C9" t="n">
-        <v>95.03</v>
+        <v>4.12</v>
       </c>
       <c r="D9" t="n">
-        <v>24189</v>
+        <v>15310</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>93.95</v>
+        <v>3.5</v>
       </c>
       <c r="B10" t="n">
-        <v>29709</v>
+        <v>37126</v>
       </c>
       <c r="C10" t="n">
-        <v>93.31999999999999</v>
+        <v>4.65</v>
       </c>
       <c r="D10" t="n">
-        <v>16294</v>
+        <v>19674</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111.38</v>
+        <v>3.99</v>
       </c>
       <c r="B11" t="n">
-        <v>27777</v>
+        <v>34793</v>
       </c>
       <c r="C11" t="n">
-        <v>113.27</v>
+        <v>6.84</v>
       </c>
       <c r="D11" t="n">
-        <v>21029</v>
+        <v>13018</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>154.7</v>
+        <v>4.13</v>
       </c>
       <c r="B12" t="n">
-        <v>23979</v>
+        <v>34995</v>
       </c>
       <c r="C12" t="n">
-        <v>159.43</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>27014</v>
+        <v>23044</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>91.97</v>
+        <v>4.93</v>
       </c>
       <c r="B13" t="n">
-        <v>24650</v>
+        <v>35168</v>
       </c>
       <c r="C13" t="n">
-        <v>87.59</v>
+        <v>5.19</v>
       </c>
       <c r="D13" t="n">
-        <v>18654</v>
+        <v>11149</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111.47</v>
+        <v>5.12</v>
       </c>
       <c r="B14" t="n">
-        <v>26410</v>
+        <v>32887</v>
       </c>
       <c r="C14" t="n">
-        <v>112.38</v>
+        <v>8.51</v>
       </c>
       <c r="D14" t="n">
-        <v>28459</v>
+        <v>27710</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111.5</v>
+        <v>5.92</v>
       </c>
       <c r="B15" t="n">
-        <v>28049</v>
+        <v>34906</v>
       </c>
       <c r="C15" t="n">
-        <v>114.15</v>
+        <v>3.61</v>
       </c>
       <c r="D15" t="n">
-        <v>28682</v>
+        <v>13561</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9.9</v>
+        <v>6.01</v>
       </c>
       <c r="B16" t="n">
-        <v>22600</v>
+        <v>34598</v>
       </c>
       <c r="C16" t="n">
-        <v>9.49</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>14024</v>
+        <v>25740</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>107.73</v>
+        <v>6.1</v>
       </c>
       <c r="B17" t="n">
-        <v>41473</v>
+        <v>33816</v>
       </c>
       <c r="C17" t="n">
-        <v>107.16</v>
+        <v>1.27</v>
       </c>
       <c r="D17" t="n">
-        <v>12609</v>
+        <v>21382</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107.36</v>
+        <v>6.4</v>
       </c>
       <c r="B18" t="n">
-        <v>39006</v>
+        <v>31989</v>
       </c>
       <c r="C18" t="n">
-        <v>107.46</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>25658</v>
+        <v>24796</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104.88</v>
+        <v>6.4</v>
       </c>
       <c r="B19" t="n">
-        <v>47343</v>
+        <v>32022</v>
       </c>
       <c r="C19" t="n">
-        <v>103.23</v>
+        <v>0.6</v>
       </c>
       <c r="D19" t="n">
-        <v>14638</v>
+        <v>26438</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112.04</v>
+        <v>6.47</v>
       </c>
       <c r="B20" t="n">
-        <v>29812</v>
+        <v>33139</v>
       </c>
       <c r="C20" t="n">
-        <v>110.47</v>
+        <v>11.41</v>
       </c>
       <c r="D20" t="n">
-        <v>27519</v>
+        <v>21296</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110.34</v>
+        <v>6.52</v>
       </c>
       <c r="B21" t="n">
-        <v>30911</v>
+        <v>33356</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>14982</v>
+        <v>14876</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>114.38</v>
+        <v>6.57</v>
       </c>
       <c r="B22" t="n">
-        <v>22736</v>
+        <v>33427</v>
       </c>
       <c r="C22" t="n">
-        <v>111.48</v>
+        <v>4.31</v>
       </c>
       <c r="D22" t="n">
-        <v>20002</v>
+        <v>27472</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110.41</v>
+        <v>6.8</v>
       </c>
       <c r="B23" t="n">
-        <v>31112</v>
+        <v>33216</v>
       </c>
       <c r="C23" t="n">
-        <v>113.92</v>
+        <v>2.72</v>
       </c>
       <c r="D23" t="n">
-        <v>24494</v>
+        <v>19591</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>107.8</v>
+        <v>6.84</v>
       </c>
       <c r="B24" t="n">
-        <v>37265</v>
+        <v>33876</v>
       </c>
       <c r="C24" t="n">
-        <v>110.26</v>
+        <v>5.9</v>
       </c>
       <c r="D24" t="n">
-        <v>19421</v>
+        <v>28210</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>107.49</v>
+        <v>7.06</v>
       </c>
       <c r="B25" t="n">
-        <v>41345</v>
+        <v>34413</v>
       </c>
       <c r="C25" t="n">
-        <v>106.04</v>
+        <v>12.53</v>
       </c>
       <c r="D25" t="n">
-        <v>20163</v>
+        <v>12097</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>92.06999999999999</v>
+        <v>7.15</v>
       </c>
       <c r="B26" t="n">
-        <v>29344</v>
+        <v>34558</v>
       </c>
       <c r="C26" t="n">
-        <v>94.47</v>
+        <v>6.7</v>
       </c>
       <c r="D26" t="n">
-        <v>27176</v>
+        <v>29050</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>114.79</v>
+        <v>7.28</v>
       </c>
       <c r="B27" t="n">
-        <v>21676</v>
+        <v>34473</v>
       </c>
       <c r="C27" t="n">
-        <v>116.7</v>
+        <v>8.31</v>
       </c>
       <c r="D27" t="n">
-        <v>15335</v>
+        <v>15984</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>95.92</v>
+        <v>7.95</v>
       </c>
       <c r="B28" t="n">
-        <v>37274</v>
+        <v>31615</v>
       </c>
       <c r="C28" t="n">
-        <v>96.31</v>
+        <v>12.39</v>
       </c>
       <c r="D28" t="n">
-        <v>14925</v>
+        <v>21659</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>92.98</v>
+        <v>8.07</v>
       </c>
       <c r="B29" t="n">
-        <v>26764</v>
+        <v>35042</v>
       </c>
       <c r="C29" t="n">
-        <v>95.8</v>
+        <v>10.93</v>
       </c>
       <c r="D29" t="n">
-        <v>23518</v>
+        <v>27276</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>97.09</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="B30" t="n">
-        <v>38934</v>
+        <v>32171</v>
       </c>
       <c r="C30" t="n">
-        <v>96.84</v>
+        <v>10.09</v>
       </c>
       <c r="D30" t="n">
-        <v>16206</v>
+        <v>14045</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>114.96</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="B31" t="n">
-        <v>24299</v>
+        <v>31137</v>
       </c>
       <c r="C31" t="n">
-        <v>112.56</v>
+        <v>10.87</v>
       </c>
       <c r="D31" t="n">
-        <v>13591</v>
+        <v>22841</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>148.38</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="B32" t="n">
-        <v>26655</v>
+        <v>31292</v>
       </c>
       <c r="C32" t="n">
-        <v>147.31</v>
+        <v>5.52</v>
       </c>
       <c r="D32" t="n">
-        <v>15082</v>
+        <v>16387</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.7</v>
+        <v>9.44</v>
       </c>
       <c r="B33" t="n">
-        <v>23222</v>
+        <v>31162</v>
       </c>
       <c r="C33" t="n">
-        <v>0.53</v>
+        <v>13.98</v>
       </c>
       <c r="D33" t="n">
-        <v>14115</v>
+        <v>23380</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>91.52</v>
+        <v>9.69</v>
       </c>
       <c r="B34" t="n">
-        <v>25974</v>
+        <v>29534</v>
       </c>
       <c r="C34" t="n">
-        <v>88.08</v>
+        <v>7.78</v>
       </c>
       <c r="D34" t="n">
-        <v>25814</v>
+        <v>11583</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>102.82</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="B35" t="n">
-        <v>46387</v>
+        <v>31271</v>
       </c>
       <c r="C35" t="n">
-        <v>105.25</v>
+        <v>18.3</v>
       </c>
       <c r="D35" t="n">
-        <v>14248</v>
+        <v>18011</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>105.64</v>
+        <v>10.1</v>
       </c>
       <c r="B36" t="n">
-        <v>44374</v>
+        <v>30855</v>
       </c>
       <c r="C36" t="n">
-        <v>106.65</v>
+        <v>13.08</v>
       </c>
       <c r="D36" t="n">
-        <v>14438</v>
+        <v>17417</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>108.8</v>
+        <v>10.29</v>
       </c>
       <c r="B37" t="n">
-        <v>37118</v>
+        <v>28559</v>
       </c>
       <c r="C37" t="n">
-        <v>105.83</v>
+        <v>12.31</v>
       </c>
       <c r="D37" t="n">
-        <v>26389</v>
+        <v>15025</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>108.21</v>
+        <v>10.82</v>
       </c>
       <c r="B38" t="n">
-        <v>36935</v>
+        <v>31938</v>
       </c>
       <c r="C38" t="n">
-        <v>107.3</v>
+        <v>17.67</v>
       </c>
       <c r="D38" t="n">
-        <v>12079</v>
+        <v>13611</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>111.57</v>
+        <v>11.05</v>
       </c>
       <c r="B39" t="n">
-        <v>28280</v>
+        <v>32158</v>
       </c>
       <c r="C39" t="n">
-        <v>109.09</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>28458</v>
+        <v>28875</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>96.04000000000001</v>
+        <v>11.08</v>
       </c>
       <c r="B40" t="n">
-        <v>38219</v>
+        <v>29890</v>
       </c>
       <c r="C40" t="n">
-        <v>97.70999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>23334</v>
+        <v>12832</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>10.71</v>
+        <v>11.46</v>
       </c>
       <c r="B41" t="n">
-        <v>25134</v>
+        <v>30254</v>
       </c>
       <c r="C41" t="n">
-        <v>10.1</v>
+        <v>11.6</v>
       </c>
       <c r="D41" t="n">
-        <v>21716</v>
+        <v>10865</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>94.8</v>
+        <v>11.69</v>
       </c>
       <c r="B42" t="n">
-        <v>34524</v>
+        <v>31176</v>
       </c>
       <c r="C42" t="n">
-        <v>95.97</v>
+        <v>17.08</v>
       </c>
       <c r="D42" t="n">
-        <v>17183</v>
+        <v>15243</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>93.11</v>
+        <v>12.14</v>
       </c>
       <c r="B43" t="n">
-        <v>30889</v>
+        <v>31267</v>
       </c>
       <c r="C43" t="n">
-        <v>91.95</v>
+        <v>9.32</v>
       </c>
       <c r="D43" t="n">
-        <v>15061</v>
+        <v>25914</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>110.27</v>
+        <v>12.21</v>
       </c>
       <c r="B44" t="n">
-        <v>33602</v>
+        <v>27251</v>
       </c>
       <c r="C44" t="n">
-        <v>113.46</v>
+        <v>15.5</v>
       </c>
       <c r="D44" t="n">
-        <v>12184</v>
+        <v>28008</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>102.61</v>
+        <v>12.43</v>
       </c>
       <c r="B45" t="n">
-        <v>46527</v>
+        <v>28434</v>
       </c>
       <c r="C45" t="n">
-        <v>103.3</v>
+        <v>6.04</v>
       </c>
       <c r="D45" t="n">
-        <v>24819</v>
+        <v>21036</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>110.58</v>
+        <v>12.61</v>
       </c>
       <c r="B46" t="n">
-        <v>33778</v>
+        <v>28087</v>
       </c>
       <c r="C46" t="n">
-        <v>109.33</v>
+        <v>11.39</v>
       </c>
       <c r="D46" t="n">
-        <v>29045</v>
+        <v>19242</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>162.19</v>
+        <v>12.78</v>
       </c>
       <c r="B47" t="n">
-        <v>22244</v>
+        <v>29990</v>
       </c>
       <c r="C47" t="n">
-        <v>155.28</v>
+        <v>12.66</v>
       </c>
       <c r="D47" t="n">
-        <v>14319</v>
+        <v>11673</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>109.18</v>
+        <v>13.08</v>
       </c>
       <c r="B48" t="n">
-        <v>33274</v>
+        <v>26098</v>
       </c>
       <c r="C48" t="n">
-        <v>113.28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>25441</v>
+        <v>18699</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>97.70999999999999</v>
+        <v>13.22</v>
       </c>
       <c r="B49" t="n">
-        <v>39402</v>
+        <v>28928</v>
       </c>
       <c r="C49" t="n">
-        <v>97.26000000000001</v>
+        <v>7.51</v>
       </c>
       <c r="D49" t="n">
-        <v>26629</v>
+        <v>18781</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>114.05</v>
+        <v>13.31</v>
       </c>
       <c r="B50" t="n">
-        <v>22630</v>
+        <v>29840</v>
       </c>
       <c r="C50" t="n">
-        <v>110.5</v>
+        <v>21.59</v>
       </c>
       <c r="D50" t="n">
-        <v>21907</v>
+        <v>25233</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>107.96</v>
+        <v>14.34</v>
       </c>
       <c r="B51" t="n">
-        <v>40359</v>
+        <v>24864</v>
       </c>
       <c r="C51" t="n">
-        <v>110.96</v>
+        <v>14.21</v>
       </c>
       <c r="D51" t="n">
-        <v>29781</v>
+        <v>21671</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>109.64</v>
+        <v>15.48</v>
       </c>
       <c r="B52" t="n">
-        <v>35116</v>
+        <v>23477</v>
       </c>
       <c r="C52" t="n">
-        <v>112.13</v>
+        <v>19.86</v>
       </c>
       <c r="D52" t="n">
-        <v>21157</v>
+        <v>19977</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>109.08</v>
+        <v>16.85</v>
       </c>
       <c r="B53" t="n">
-        <v>33840</v>
+        <v>25131</v>
       </c>
       <c r="C53" t="n">
-        <v>111.12</v>
+        <v>10.39</v>
       </c>
       <c r="D53" t="n">
-        <v>17952</v>
+        <v>24103</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>90.06</v>
+        <v>17.47</v>
       </c>
       <c r="B54" t="n">
-        <v>24274</v>
+        <v>24727</v>
       </c>
       <c r="C54" t="n">
-        <v>89.26000000000001</v>
+        <v>25.94</v>
       </c>
       <c r="D54" t="n">
-        <v>25390</v>
+        <v>26608</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>93.89</v>
+        <v>18.3</v>
       </c>
       <c r="B55" t="n">
-        <v>30963</v>
+        <v>26051</v>
       </c>
       <c r="C55" t="n">
-        <v>91.31999999999999</v>
+        <v>20.26</v>
       </c>
       <c r="D55" t="n">
-        <v>19461</v>
+        <v>13324</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>26.09</v>
+        <v>19.1</v>
       </c>
       <c r="B56" t="n">
-        <v>23998</v>
+        <v>23430</v>
       </c>
       <c r="C56" t="n">
-        <v>26.22</v>
+        <v>23.2</v>
       </c>
       <c r="D56" t="n">
-        <v>21924</v>
+        <v>19876</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>109.74</v>
+        <v>19.14</v>
       </c>
       <c r="B57" t="n">
-        <v>34516</v>
+        <v>26432</v>
       </c>
       <c r="C57" t="n">
-        <v>108.76</v>
+        <v>15.05</v>
       </c>
       <c r="D57" t="n">
-        <v>19161</v>
+        <v>23972</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>100.88</v>
+        <v>19.21</v>
       </c>
       <c r="B58" t="n">
-        <v>43464</v>
+        <v>25183</v>
       </c>
       <c r="C58" t="n">
-        <v>96.90000000000001</v>
+        <v>30.11</v>
       </c>
       <c r="D58" t="n">
-        <v>23067</v>
+        <v>16585</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>108.23</v>
+        <v>20.07</v>
       </c>
       <c r="B59" t="n">
-        <v>36195</v>
+        <v>21473</v>
       </c>
       <c r="C59" t="n">
-        <v>108.61</v>
+        <v>24.3</v>
       </c>
       <c r="D59" t="n">
-        <v>11414</v>
+        <v>24096</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>173.16</v>
+        <v>20.74</v>
       </c>
       <c r="B60" t="n">
-        <v>25685</v>
+        <v>23719</v>
       </c>
       <c r="C60" t="n">
-        <v>176.56</v>
+        <v>20.83</v>
       </c>
       <c r="D60" t="n">
-        <v>27525</v>
+        <v>21912</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>94.25</v>
+        <v>21.04</v>
       </c>
       <c r="B61" t="n">
-        <v>30847</v>
+        <v>22223</v>
       </c>
       <c r="C61" t="n">
-        <v>91.62</v>
+        <v>18.78</v>
       </c>
       <c r="D61" t="n">
-        <v>15178</v>
+        <v>12496</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>97.56</v>
+        <v>21.12</v>
       </c>
       <c r="B62" t="n">
-        <v>42050</v>
+        <v>21359</v>
       </c>
       <c r="C62" t="n">
-        <v>100.58</v>
+        <v>16.26</v>
       </c>
       <c r="D62" t="n">
-        <v>20050</v>
+        <v>16603</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>109.24</v>
+        <v>21.33</v>
       </c>
       <c r="B63" t="n">
-        <v>34318</v>
+        <v>24681</v>
       </c>
       <c r="C63" t="n">
-        <v>108.22</v>
+        <v>29.75</v>
       </c>
       <c r="D63" t="n">
-        <v>10612</v>
+        <v>29402</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>97.77</v>
+        <v>21.44</v>
       </c>
       <c r="B64" t="n">
-        <v>41907</v>
+        <v>24196</v>
       </c>
       <c r="C64" t="n">
-        <v>101.32</v>
+        <v>14.61</v>
       </c>
       <c r="D64" t="n">
-        <v>28893</v>
+        <v>24742</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>108.23</v>
+        <v>21.79</v>
       </c>
       <c r="B65" t="n">
-        <v>37049</v>
+        <v>23136</v>
       </c>
       <c r="C65" t="n">
-        <v>108.7</v>
+        <v>19.45</v>
       </c>
       <c r="D65" t="n">
-        <v>19274</v>
+        <v>27075</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>107.35</v>
+        <v>21.87</v>
       </c>
       <c r="B66" t="n">
-        <v>41206</v>
+        <v>24188</v>
       </c>
       <c r="C66" t="n">
-        <v>105.79</v>
+        <v>15.67</v>
       </c>
       <c r="D66" t="n">
-        <v>28418</v>
+        <v>15227</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>169.76</v>
+        <v>21.98</v>
       </c>
       <c r="B67" t="n">
-        <v>23525</v>
+        <v>24455</v>
       </c>
       <c r="C67" t="n">
-        <v>163.56</v>
+        <v>29.45</v>
       </c>
       <c r="D67" t="n">
-        <v>11950</v>
+        <v>15618</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>98.13</v>
+        <v>22.02</v>
       </c>
       <c r="B68" t="n">
-        <v>42437</v>
+        <v>23972</v>
       </c>
       <c r="C68" t="n">
-        <v>97.41</v>
+        <v>17.04</v>
       </c>
       <c r="D68" t="n">
-        <v>25775</v>
+        <v>10916</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>102.43</v>
+        <v>22.78</v>
       </c>
       <c r="B69" t="n">
-        <v>48915</v>
+        <v>24054</v>
       </c>
       <c r="C69" t="n">
-        <v>98.59</v>
+        <v>25.34</v>
       </c>
       <c r="D69" t="n">
-        <v>12855</v>
+        <v>20700</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>78.68000000000001</v>
+        <v>22.81</v>
       </c>
       <c r="B70" t="n">
-        <v>22863</v>
+        <v>22254</v>
       </c>
       <c r="C70" t="n">
-        <v>80.94</v>
+        <v>22.09</v>
       </c>
       <c r="D70" t="n">
-        <v>14338</v>
+        <v>22484</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>106.35</v>
+        <v>23.13</v>
       </c>
       <c r="B71" t="n">
-        <v>44542</v>
+        <v>22425</v>
       </c>
       <c r="C71" t="n">
-        <v>110.19</v>
+        <v>11.95</v>
       </c>
       <c r="D71" t="n">
-        <v>24311</v>
+        <v>28336</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>111.34</v>
+        <v>23.39</v>
       </c>
       <c r="B72" t="n">
-        <v>27309</v>
+        <v>24308</v>
       </c>
       <c r="C72" t="n">
-        <v>107.47</v>
+        <v>28.62</v>
       </c>
       <c r="D72" t="n">
-        <v>12972</v>
+        <v>11434</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>92.01000000000001</v>
+        <v>23.76</v>
       </c>
       <c r="B73" t="n">
-        <v>25072</v>
+        <v>22255</v>
       </c>
       <c r="C73" t="n">
-        <v>89.58</v>
+        <v>20.65</v>
       </c>
       <c r="D73" t="n">
-        <v>29107</v>
+        <v>29223</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113.49</v>
+        <v>24.09</v>
       </c>
       <c r="B74" t="n">
-        <v>24473</v>
+        <v>21939</v>
       </c>
       <c r="C74" t="n">
-        <v>116.59</v>
+        <v>31.7</v>
       </c>
       <c r="D74" t="n">
-        <v>14046</v>
+        <v>25751</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>167.96</v>
+        <v>24.46</v>
       </c>
       <c r="B75" t="n">
-        <v>22611</v>
+        <v>22275</v>
       </c>
       <c r="C75" t="n">
-        <v>161.91</v>
+        <v>25.56</v>
       </c>
       <c r="D75" t="n">
-        <v>11165</v>
+        <v>29595</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>95.45</v>
+        <v>24.61</v>
       </c>
       <c r="B76" t="n">
-        <v>35620</v>
+        <v>26085</v>
       </c>
       <c r="C76" t="n">
-        <v>96.79000000000001</v>
+        <v>19.16</v>
       </c>
       <c r="D76" t="n">
-        <v>11038</v>
+        <v>10532</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>91.81999999999999</v>
+        <v>24.88</v>
       </c>
       <c r="B77" t="n">
-        <v>25979</v>
+        <v>23881</v>
       </c>
       <c r="C77" t="n">
-        <v>94.09</v>
+        <v>32.35</v>
       </c>
       <c r="D77" t="n">
-        <v>20962</v>
+        <v>22170</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>154.65</v>
+        <v>25.5</v>
       </c>
       <c r="B78" t="n">
-        <v>21780</v>
+        <v>20804</v>
       </c>
       <c r="C78" t="n">
-        <v>151.41</v>
+        <v>25.02</v>
       </c>
       <c r="D78" t="n">
-        <v>27556</v>
+        <v>27694</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>110.7</v>
+        <v>25.68</v>
       </c>
       <c r="B79" t="n">
-        <v>29455</v>
+        <v>22916</v>
       </c>
       <c r="C79" t="n">
-        <v>106.01</v>
+        <v>27.58</v>
       </c>
       <c r="D79" t="n">
-        <v>17903</v>
+        <v>24921</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>107.38</v>
+        <v>25.89</v>
       </c>
       <c r="B80" t="n">
-        <v>40155</v>
+        <v>21776</v>
       </c>
       <c r="C80" t="n">
-        <v>109.91</v>
+        <v>29.15</v>
       </c>
       <c r="D80" t="n">
-        <v>22724</v>
+        <v>24346</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>106.79</v>
+        <v>26.47</v>
       </c>
       <c r="B81" t="n">
-        <v>43403</v>
+        <v>20627</v>
       </c>
       <c r="C81" t="n">
-        <v>104.89</v>
+        <v>22.4</v>
       </c>
       <c r="D81" t="n">
-        <v>29778</v>
+        <v>22028</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>106.51</v>
+        <v>26.49</v>
       </c>
       <c r="B82" t="n">
-        <v>42500</v>
+        <v>20612</v>
       </c>
       <c r="C82" t="n">
-        <v>108.69</v>
+        <v>39.67</v>
       </c>
       <c r="D82" t="n">
-        <v>17561</v>
+        <v>24471</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>94.94</v>
+        <v>26.72</v>
       </c>
       <c r="B83" t="n">
-        <v>34171</v>
+        <v>22380</v>
       </c>
       <c r="C83" t="n">
-        <v>93.34999999999999</v>
+        <v>35.96</v>
       </c>
       <c r="D83" t="n">
-        <v>11309</v>
+        <v>15874</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>105.68</v>
+        <v>26.88</v>
       </c>
       <c r="B84" t="n">
-        <v>44566</v>
+        <v>22255</v>
       </c>
       <c r="C84" t="n">
-        <v>103.95</v>
+        <v>28.33</v>
       </c>
       <c r="D84" t="n">
-        <v>13788</v>
+        <v>22527</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>102.5</v>
+        <v>26.88</v>
       </c>
       <c r="B85" t="n">
-        <v>43158</v>
+        <v>19946</v>
       </c>
       <c r="C85" t="n">
-        <v>105.07</v>
+        <v>16.97</v>
       </c>
       <c r="D85" t="n">
-        <v>17174</v>
+        <v>17064</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>93.90000000000001</v>
+        <v>26.9</v>
       </c>
       <c r="B86" t="n">
-        <v>29729</v>
+        <v>20364</v>
       </c>
       <c r="C86" t="n">
-        <v>90.04000000000001</v>
+        <v>22.36</v>
       </c>
       <c r="D86" t="n">
-        <v>19884</v>
+        <v>29823</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128.05</v>
+        <v>27.32</v>
       </c>
       <c r="B87" t="n">
-        <v>22456</v>
+        <v>19351</v>
       </c>
       <c r="C87" t="n">
-        <v>124.98</v>
+        <v>32.46</v>
       </c>
       <c r="D87" t="n">
-        <v>26317</v>
+        <v>16995</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>96.39</v>
+        <v>27.4</v>
       </c>
       <c r="B88" t="n">
-        <v>37559</v>
+        <v>23241</v>
       </c>
       <c r="C88" t="n">
-        <v>99.69</v>
+        <v>28.45</v>
       </c>
       <c r="D88" t="n">
-        <v>22244</v>
+        <v>11243</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>100.35</v>
+        <v>27.49</v>
       </c>
       <c r="B89" t="n">
-        <v>46739</v>
+        <v>24064</v>
       </c>
       <c r="C89" t="n">
-        <v>99.79000000000001</v>
+        <v>28.19</v>
       </c>
       <c r="D89" t="n">
-        <v>19132</v>
+        <v>23737</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>25.77</v>
+        <v>27.72</v>
       </c>
       <c r="B90" t="n">
-        <v>25530</v>
+        <v>22751</v>
       </c>
       <c r="C90" t="n">
-        <v>25.7</v>
+        <v>29.75</v>
       </c>
       <c r="D90" t="n">
-        <v>25245</v>
+        <v>12642</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>103.86</v>
+        <v>28</v>
       </c>
       <c r="B91" t="n">
-        <v>47621</v>
+        <v>19913</v>
       </c>
       <c r="C91" t="n">
-        <v>102.08</v>
+        <v>38.79</v>
       </c>
       <c r="D91" t="n">
-        <v>27762</v>
+        <v>20814</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>99.86</v>
+        <v>28.12</v>
       </c>
       <c r="B92" t="n">
-        <v>43977</v>
+        <v>22964</v>
       </c>
       <c r="C92" t="n">
-        <v>99.03</v>
+        <v>29.69</v>
       </c>
       <c r="D92" t="n">
-        <v>21401</v>
+        <v>28159</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>111.27</v>
+        <v>28.17</v>
       </c>
       <c r="B93" t="n">
-        <v>28185</v>
+        <v>22115</v>
       </c>
       <c r="C93" t="n">
-        <v>115.5</v>
+        <v>23.89</v>
       </c>
       <c r="D93" t="n">
-        <v>21221</v>
+        <v>13004</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>69.53</v>
+        <v>28.17</v>
       </c>
       <c r="B94" t="n">
-        <v>23753</v>
+        <v>23839</v>
       </c>
       <c r="C94" t="n">
-        <v>71.48999999999999</v>
+        <v>20.37</v>
       </c>
       <c r="D94" t="n">
-        <v>24637</v>
+        <v>11976</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>113.93</v>
+        <v>28.24</v>
       </c>
       <c r="B95" t="n">
-        <v>23151</v>
+        <v>19739</v>
       </c>
       <c r="C95" t="n">
-        <v>112.48</v>
+        <v>29.39</v>
       </c>
       <c r="D95" t="n">
-        <v>26244</v>
+        <v>13666</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>91.31</v>
+        <v>28.27</v>
       </c>
       <c r="B96" t="n">
-        <v>25107</v>
+        <v>21914</v>
       </c>
       <c r="C96" t="n">
-        <v>90.38</v>
+        <v>29.47</v>
       </c>
       <c r="D96" t="n">
-        <v>20476</v>
+        <v>11577</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>106.92</v>
+        <v>28.7</v>
       </c>
       <c r="B97" t="n">
-        <v>42071</v>
+        <v>22061</v>
       </c>
       <c r="C97" t="n">
-        <v>104.3</v>
+        <v>22.25</v>
       </c>
       <c r="D97" t="n">
-        <v>22976</v>
+        <v>27223</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>102.45</v>
+        <v>28.72</v>
       </c>
       <c r="B98" t="n">
-        <v>49193</v>
+        <v>21204</v>
       </c>
       <c r="C98" t="n">
-        <v>106.23</v>
+        <v>25.17</v>
       </c>
       <c r="D98" t="n">
-        <v>10531</v>
+        <v>18649</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>102.31</v>
+        <v>28.77</v>
       </c>
       <c r="B99" t="n">
-        <v>46804</v>
+        <v>21595</v>
       </c>
       <c r="C99" t="n">
-        <v>105.01</v>
+        <v>25.6</v>
       </c>
       <c r="D99" t="n">
-        <v>26480</v>
+        <v>18589</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>90.92</v>
+        <v>28.8</v>
       </c>
       <c r="B100" t="n">
-        <v>23171</v>
+        <v>18514</v>
       </c>
       <c r="C100" t="n">
-        <v>91.84999999999999</v>
+        <v>21.6</v>
       </c>
       <c r="D100" t="n">
-        <v>20276</v>
+        <v>28602</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>4.07</v>
+        <v>29.38</v>
       </c>
       <c r="B101" t="n">
-        <v>22007</v>
+        <v>20745</v>
       </c>
       <c r="C101" t="n">
-        <v>3.26</v>
+        <v>19.37</v>
       </c>
       <c r="D101" t="n">
-        <v>27168</v>
+        <v>12618</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>92.44</v>
+        <v>29.58</v>
       </c>
       <c r="B102" t="n">
-        <v>26351</v>
+        <v>23179</v>
       </c>
       <c r="C102" t="n">
-        <v>90.36</v>
+        <v>32.35</v>
       </c>
       <c r="D102" t="n">
-        <v>18013</v>
+        <v>21989</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>105.71</v>
+        <v>29.65</v>
       </c>
       <c r="B103" t="n">
-        <v>45895</v>
+        <v>20199</v>
       </c>
       <c r="C103" t="n">
-        <v>107.69</v>
+        <v>31.2</v>
       </c>
       <c r="D103" t="n">
-        <v>23309</v>
+        <v>13432</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>105.88</v>
+        <v>31.2</v>
       </c>
       <c r="B104" t="n">
-        <v>43888</v>
+        <v>21494</v>
       </c>
       <c r="C104" t="n">
-        <v>103.27</v>
+        <v>34.63</v>
       </c>
       <c r="D104" t="n">
-        <v>25340</v>
+        <v>24368</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>90.18000000000001</v>
+        <v>31.78</v>
       </c>
       <c r="B105" t="n">
-        <v>24199</v>
+        <v>19198</v>
       </c>
       <c r="C105" t="n">
-        <v>90.26000000000001</v>
+        <v>40.05</v>
       </c>
       <c r="D105" t="n">
-        <v>12305</v>
+        <v>17399</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>102.18</v>
+        <v>31.92</v>
       </c>
       <c r="B106" t="n">
-        <v>45707</v>
+        <v>18852</v>
       </c>
       <c r="C106" t="n">
-        <v>98.93000000000001</v>
+        <v>26.9</v>
       </c>
       <c r="D106" t="n">
-        <v>19025</v>
+        <v>14728</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>17.58</v>
+        <v>32.99</v>
       </c>
       <c r="B107" t="n">
-        <v>21785</v>
+        <v>21791</v>
       </c>
       <c r="C107" t="n">
-        <v>17.81</v>
+        <v>37.43</v>
       </c>
       <c r="D107" t="n">
-        <v>24204</v>
+        <v>11962</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>100.3</v>
+        <v>33.53</v>
       </c>
       <c r="B108" t="n">
-        <v>45414</v>
+        <v>22573</v>
       </c>
       <c r="C108" t="n">
-        <v>104.34</v>
+        <v>40.55</v>
       </c>
       <c r="D108" t="n">
-        <v>27199</v>
+        <v>15569</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>53.59</v>
+        <v>33.8</v>
       </c>
       <c r="B109" t="n">
-        <v>24280</v>
+        <v>21146</v>
       </c>
       <c r="C109" t="n">
-        <v>53.62</v>
+        <v>38</v>
       </c>
       <c r="D109" t="n">
-        <v>21558</v>
+        <v>11219</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>105.93</v>
+        <v>34.33</v>
       </c>
       <c r="B110" t="n">
-        <v>44775</v>
+        <v>22088</v>
       </c>
       <c r="C110" t="n">
-        <v>103.75</v>
+        <v>35.92</v>
       </c>
       <c r="D110" t="n">
-        <v>27764</v>
+        <v>27164</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>100.52</v>
+        <v>34.46</v>
       </c>
       <c r="B111" t="n">
-        <v>44526</v>
+        <v>20033</v>
       </c>
       <c r="C111" t="n">
-        <v>104.07</v>
+        <v>42.51</v>
       </c>
       <c r="D111" t="n">
-        <v>11428</v>
+        <v>11793</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>103.25</v>
+        <v>34.58</v>
       </c>
       <c r="B112" t="n">
-        <v>49231</v>
+        <v>22289</v>
       </c>
       <c r="C112" t="n">
-        <v>103.11</v>
+        <v>37.56</v>
       </c>
       <c r="D112" t="n">
-        <v>28117</v>
+        <v>29787</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>112.66</v>
+        <v>35.06</v>
       </c>
       <c r="B113" t="n">
-        <v>24900</v>
+        <v>20913</v>
       </c>
       <c r="C113" t="n">
-        <v>111.11</v>
+        <v>36.67</v>
       </c>
       <c r="D113" t="n">
-        <v>10054</v>
+        <v>24482</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>97.7</v>
+        <v>36.42</v>
       </c>
       <c r="B114" t="n">
-        <v>40815</v>
+        <v>22487</v>
       </c>
       <c r="C114" t="n">
-        <v>94.75</v>
+        <v>47.56</v>
       </c>
       <c r="D114" t="n">
-        <v>23594</v>
+        <v>25682</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>108.65</v>
+        <v>36.43</v>
       </c>
       <c r="B115" t="n">
-        <v>37343</v>
+        <v>22612</v>
       </c>
       <c r="C115" t="n">
-        <v>111.89</v>
+        <v>34.39</v>
       </c>
       <c r="D115" t="n">
-        <v>23985</v>
+        <v>28861</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>98.15000000000001</v>
+        <v>36.74</v>
       </c>
       <c r="B116" t="n">
-        <v>42059</v>
+        <v>22023</v>
       </c>
       <c r="C116" t="n">
-        <v>96.73</v>
+        <v>39</v>
       </c>
       <c r="D116" t="n">
-        <v>14075</v>
+        <v>19708</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>99.88</v>
+        <v>37.07</v>
       </c>
       <c r="B117" t="n">
-        <v>45714</v>
+        <v>21013</v>
       </c>
       <c r="C117" t="n">
-        <v>98.87</v>
+        <v>36.39</v>
       </c>
       <c r="D117" t="n">
-        <v>22998</v>
+        <v>17045</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>154.02</v>
+        <v>37.08</v>
       </c>
       <c r="B118" t="n">
-        <v>23797</v>
+        <v>22243</v>
       </c>
       <c r="C118" t="n">
-        <v>155.59</v>
+        <v>42.77</v>
       </c>
       <c r="D118" t="n">
-        <v>15522</v>
+        <v>19897</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>99.41</v>
+        <v>37.33</v>
       </c>
       <c r="B119" t="n">
-        <v>44927</v>
+        <v>22044</v>
       </c>
       <c r="C119" t="n">
-        <v>98.31</v>
+        <v>34</v>
       </c>
       <c r="D119" t="n">
-        <v>20407</v>
+        <v>23418</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>101.34</v>
+        <v>37.45</v>
       </c>
       <c r="B120" t="n">
-        <v>45661</v>
+        <v>22318</v>
       </c>
       <c r="C120" t="n">
-        <v>104.18</v>
+        <v>39.43</v>
       </c>
       <c r="D120" t="n">
-        <v>28451</v>
+        <v>28203</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>106.38</v>
+        <v>37.72</v>
       </c>
       <c r="B121" t="n">
-        <v>42540</v>
+        <v>21627</v>
       </c>
       <c r="C121" t="n">
-        <v>109.92</v>
+        <v>30.09</v>
       </c>
       <c r="D121" t="n">
-        <v>12950</v>
+        <v>21738</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>94.59</v>
+        <v>37.86</v>
       </c>
       <c r="B122" t="n">
-        <v>30480</v>
+        <v>17960</v>
       </c>
       <c r="C122" t="n">
-        <v>94.34999999999999</v>
+        <v>38.76</v>
       </c>
       <c r="D122" t="n">
-        <v>25977</v>
+        <v>16031</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>98.18000000000001</v>
+        <v>40.86</v>
       </c>
       <c r="B123" t="n">
-        <v>42588</v>
+        <v>21961</v>
       </c>
       <c r="C123" t="n">
-        <v>97.05</v>
+        <v>37.74</v>
       </c>
       <c r="D123" t="n">
-        <v>25118</v>
+        <v>14715</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>105.01</v>
+        <v>40.95</v>
       </c>
       <c r="B124" t="n">
-        <v>48002</v>
+        <v>20948</v>
       </c>
       <c r="C124" t="n">
-        <v>108.79</v>
+        <v>39.74</v>
       </c>
       <c r="D124" t="n">
-        <v>12685</v>
+        <v>25824</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>90.63</v>
+        <v>41.32</v>
       </c>
       <c r="B125" t="n">
-        <v>25416</v>
+        <v>19530</v>
       </c>
       <c r="C125" t="n">
-        <v>89.62</v>
+        <v>37.88</v>
       </c>
       <c r="D125" t="n">
-        <v>22603</v>
+        <v>28354</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>94.29000000000001</v>
+        <v>42.89</v>
       </c>
       <c r="B126" t="n">
-        <v>31999</v>
+        <v>19954</v>
       </c>
       <c r="C126" t="n">
-        <v>91.95999999999999</v>
+        <v>42.38</v>
       </c>
       <c r="D126" t="n">
-        <v>26835</v>
+        <v>26616</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>109.38</v>
+        <v>43.77</v>
       </c>
       <c r="B127" t="n">
-        <v>33076</v>
+        <v>19937</v>
       </c>
       <c r="C127" t="n">
-        <v>105.26</v>
+        <v>28.5</v>
       </c>
       <c r="D127" t="n">
-        <v>17557</v>
+        <v>26470</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>90.19</v>
+        <v>44.62</v>
       </c>
       <c r="B128" t="n">
-        <v>20683</v>
+        <v>20268</v>
       </c>
       <c r="C128" t="n">
-        <v>89.39</v>
+        <v>41.72</v>
       </c>
       <c r="D128" t="n">
-        <v>27103</v>
+        <v>29540</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>100.34</v>
+        <v>44.74</v>
       </c>
       <c r="B129" t="n">
-        <v>43998</v>
+        <v>21704</v>
       </c>
       <c r="C129" t="n">
-        <v>97.26000000000001</v>
+        <v>47.79</v>
       </c>
       <c r="D129" t="n">
-        <v>14634</v>
+        <v>26420</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>100.94</v>
+        <v>44.97</v>
       </c>
       <c r="B130" t="n">
-        <v>46003</v>
+        <v>20688</v>
       </c>
       <c r="C130" t="n">
-        <v>99.90000000000001</v>
+        <v>38</v>
       </c>
       <c r="D130" t="n">
-        <v>27686</v>
+        <v>17745</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>97.67</v>
+        <v>45.72</v>
       </c>
       <c r="B131" t="n">
-        <v>45628</v>
+        <v>20510</v>
       </c>
       <c r="C131" t="n">
-        <v>97.64</v>
+        <v>59.3</v>
       </c>
       <c r="D131" t="n">
-        <v>20980</v>
+        <v>24397</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>106.2</v>
+        <v>45.87</v>
       </c>
       <c r="B132" t="n">
-        <v>44011</v>
+        <v>20572</v>
       </c>
       <c r="C132" t="n">
-        <v>103.49</v>
+        <v>38.39</v>
       </c>
       <c r="D132" t="n">
-        <v>13622</v>
+        <v>22358</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>90.59999999999999</v>
+        <v>46.01</v>
       </c>
       <c r="B133" t="n">
-        <v>25922</v>
+        <v>21425</v>
       </c>
       <c r="C133" t="n">
-        <v>90.54000000000001</v>
+        <v>41.14</v>
       </c>
       <c r="D133" t="n">
-        <v>21764</v>
+        <v>14468</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>114.95</v>
+        <v>46.13</v>
       </c>
       <c r="B134" t="n">
-        <v>23136</v>
+        <v>20920</v>
       </c>
       <c r="C134" t="n">
-        <v>114.45</v>
+        <v>34.29</v>
       </c>
       <c r="D134" t="n">
-        <v>10315</v>
+        <v>25906</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>83.17</v>
+        <v>46.4</v>
       </c>
       <c r="B135" t="n">
-        <v>22355</v>
+        <v>20861</v>
       </c>
       <c r="C135" t="n">
-        <v>83.3</v>
+        <v>46.66</v>
       </c>
       <c r="D135" t="n">
-        <v>14223</v>
+        <v>16239</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>70.12</v>
+        <v>46.54</v>
       </c>
       <c r="B136" t="n">
-        <v>21601</v>
+        <v>20012</v>
       </c>
       <c r="C136" t="n">
-        <v>67.06</v>
+        <v>53.38</v>
       </c>
       <c r="D136" t="n">
-        <v>25625</v>
+        <v>14919</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>98.63</v>
+        <v>46.75</v>
       </c>
       <c r="B137" t="n">
-        <v>41056</v>
+        <v>21688</v>
       </c>
       <c r="C137" t="n">
-        <v>97.89</v>
+        <v>49.62</v>
       </c>
       <c r="D137" t="n">
-        <v>13513</v>
+        <v>22129</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>75.08</v>
+        <v>47.48</v>
       </c>
       <c r="B138" t="n">
-        <v>20709</v>
+        <v>21614</v>
       </c>
       <c r="C138" t="n">
-        <v>74.90000000000001</v>
+        <v>49.05</v>
       </c>
       <c r="D138" t="n">
-        <v>23120</v>
+        <v>15503</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>154.73</v>
+        <v>47.53</v>
       </c>
       <c r="B139" t="n">
-        <v>25144</v>
+        <v>21707</v>
       </c>
       <c r="C139" t="n">
-        <v>149.18</v>
+        <v>52.71</v>
       </c>
       <c r="D139" t="n">
-        <v>21972</v>
+        <v>23958</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>151.1</v>
+        <v>47.97</v>
       </c>
       <c r="B140" t="n">
-        <v>23855</v>
+        <v>21318</v>
       </c>
       <c r="C140" t="n">
-        <v>149.91</v>
+        <v>51.67</v>
       </c>
       <c r="D140" t="n">
-        <v>26516</v>
+        <v>11035</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>110.45</v>
+        <v>48.57</v>
       </c>
       <c r="B141" t="n">
-        <v>31817</v>
+        <v>21825</v>
       </c>
       <c r="C141" t="n">
-        <v>106.03</v>
+        <v>37.12</v>
       </c>
       <c r="D141" t="n">
-        <v>11521</v>
+        <v>25481</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>90.34999999999999</v>
+        <v>48.79</v>
       </c>
       <c r="B142" t="n">
-        <v>23925</v>
+        <v>20228</v>
       </c>
       <c r="C142" t="n">
-        <v>89.90000000000001</v>
+        <v>56.77</v>
       </c>
       <c r="D142" t="n">
-        <v>14879</v>
+        <v>28144</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>108.22</v>
+        <v>49.26</v>
       </c>
       <c r="B143" t="n">
-        <v>37108</v>
+        <v>22187</v>
       </c>
       <c r="C143" t="n">
-        <v>105.99</v>
+        <v>49.59</v>
       </c>
       <c r="D143" t="n">
-        <v>13593</v>
+        <v>27530</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>179.83</v>
+        <v>50.33</v>
       </c>
       <c r="B144" t="n">
-        <v>25464</v>
+        <v>21296</v>
       </c>
       <c r="C144" t="n">
-        <v>173.21</v>
+        <v>44.17</v>
       </c>
       <c r="D144" t="n">
-        <v>26919</v>
+        <v>14768</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>102.2</v>
+        <v>50.73</v>
       </c>
       <c r="B145" t="n">
-        <v>46382</v>
+        <v>20976</v>
       </c>
       <c r="C145" t="n">
-        <v>98.98</v>
+        <v>59.42</v>
       </c>
       <c r="D145" t="n">
-        <v>16630</v>
+        <v>18358</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>90.52</v>
+        <v>50.77</v>
       </c>
       <c r="B146" t="n">
-        <v>24043</v>
+        <v>20278</v>
       </c>
       <c r="C146" t="n">
-        <v>93.3</v>
+        <v>47.73</v>
       </c>
       <c r="D146" t="n">
-        <v>21215</v>
+        <v>24953</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>173.35</v>
+        <v>50.95</v>
       </c>
       <c r="B147" t="n">
-        <v>26789</v>
+        <v>20965</v>
       </c>
       <c r="C147" t="n">
-        <v>174.35</v>
+        <v>52.41</v>
       </c>
       <c r="D147" t="n">
-        <v>18685</v>
+        <v>14927</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>111.85</v>
+        <v>51.12</v>
       </c>
       <c r="B148" t="n">
-        <v>28292</v>
+        <v>21045</v>
       </c>
       <c r="C148" t="n">
-        <v>110.74</v>
+        <v>53.6</v>
       </c>
       <c r="D148" t="n">
-        <v>21943</v>
+        <v>19673</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>103.67</v>
+        <v>51.13</v>
       </c>
       <c r="B149" t="n">
-        <v>47027</v>
+        <v>22131</v>
       </c>
       <c r="C149" t="n">
-        <v>106.73</v>
+        <v>60.5</v>
       </c>
       <c r="D149" t="n">
-        <v>22708</v>
+        <v>28082</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>94.38</v>
+        <v>51.28</v>
       </c>
       <c r="B150" t="n">
-        <v>34291</v>
+        <v>21106</v>
       </c>
       <c r="C150" t="n">
-        <v>90.61</v>
+        <v>52.67</v>
       </c>
       <c r="D150" t="n">
-        <v>11002</v>
+        <v>14360</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>67.51000000000001</v>
+        <v>51.69</v>
       </c>
       <c r="B151" t="n">
-        <v>25155</v>
+        <v>20905</v>
       </c>
       <c r="C151" t="n">
-        <v>65.37</v>
+        <v>56.71</v>
       </c>
       <c r="D151" t="n">
-        <v>10647</v>
+        <v>24143</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>109.23</v>
+        <v>51.9</v>
       </c>
       <c r="B152" t="n">
-        <v>35861</v>
+        <v>20947</v>
       </c>
       <c r="C152" t="n">
-        <v>113.38</v>
+        <v>54.43</v>
       </c>
       <c r="D152" t="n">
-        <v>19532</v>
+        <v>11760</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>110.34</v>
+        <v>51.96</v>
       </c>
       <c r="B153" t="n">
-        <v>29615</v>
+        <v>20123</v>
       </c>
       <c r="C153" t="n">
-        <v>109.32</v>
+        <v>50.05</v>
       </c>
       <c r="D153" t="n">
-        <v>23524</v>
+        <v>21134</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>106.42</v>
+        <v>52.25</v>
       </c>
       <c r="B154" t="n">
-        <v>42928</v>
+        <v>22305</v>
       </c>
       <c r="C154" t="n">
-        <v>105.44</v>
+        <v>47.53</v>
       </c>
       <c r="D154" t="n">
-        <v>19452</v>
+        <v>26695</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>113.28</v>
+        <v>52.68</v>
       </c>
       <c r="B155" t="n">
-        <v>24669</v>
+        <v>20623</v>
       </c>
       <c r="C155" t="n">
-        <v>112.47</v>
+        <v>48.4</v>
       </c>
       <c r="D155" t="n">
-        <v>18204</v>
+        <v>28793</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>99.43000000000001</v>
+        <v>53.65</v>
       </c>
       <c r="B156" t="n">
-        <v>42551</v>
+        <v>19173</v>
       </c>
       <c r="C156" t="n">
-        <v>100.15</v>
+        <v>61.06</v>
       </c>
       <c r="D156" t="n">
-        <v>26594</v>
+        <v>27524</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>107.92</v>
+        <v>54.06</v>
       </c>
       <c r="B157" t="n">
-        <v>37998</v>
+        <v>21821</v>
       </c>
       <c r="C157" t="n">
-        <v>106.64</v>
+        <v>61.94</v>
       </c>
       <c r="D157" t="n">
-        <v>19969</v>
+        <v>20183</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>102.21</v>
+        <v>55.37</v>
       </c>
       <c r="B158" t="n">
-        <v>47152</v>
+        <v>19809</v>
       </c>
       <c r="C158" t="n">
-        <v>102.23</v>
+        <v>51.45</v>
       </c>
       <c r="D158" t="n">
-        <v>11274</v>
+        <v>10867</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>97.13</v>
+        <v>55.47</v>
       </c>
       <c r="B159" t="n">
-        <v>38079</v>
+        <v>20238</v>
       </c>
       <c r="C159" t="n">
-        <v>98.06</v>
+        <v>59.67</v>
       </c>
       <c r="D159" t="n">
-        <v>15357</v>
+        <v>18485</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>101.24</v>
+        <v>55.53</v>
       </c>
       <c r="B160" t="n">
-        <v>44830</v>
+        <v>20245</v>
       </c>
       <c r="C160" t="n">
-        <v>104.04</v>
+        <v>62.03</v>
       </c>
       <c r="D160" t="n">
-        <v>11240</v>
+        <v>22059</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>92.79000000000001</v>
+        <v>55.77</v>
       </c>
       <c r="B161" t="n">
-        <v>28481</v>
+        <v>21251</v>
       </c>
       <c r="C161" t="n">
-        <v>89.95999999999999</v>
+        <v>68.63</v>
       </c>
       <c r="D161" t="n">
-        <v>27779</v>
+        <v>11905</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>115.68</v>
+        <v>55.98</v>
       </c>
       <c r="B162" t="n">
-        <v>23089</v>
+        <v>19894</v>
       </c>
       <c r="C162" t="n">
-        <v>118.33</v>
+        <v>64.69</v>
       </c>
       <c r="D162" t="n">
-        <v>28687</v>
+        <v>23565</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>110.89</v>
+        <v>56.02</v>
       </c>
       <c r="B163" t="n">
-        <v>30394</v>
+        <v>21617</v>
       </c>
       <c r="C163" t="n">
-        <v>113.41</v>
+        <v>63.1</v>
       </c>
       <c r="D163" t="n">
-        <v>22497</v>
+        <v>16351</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>104.83</v>
+        <v>56.14</v>
       </c>
       <c r="B164" t="n">
-        <v>42840</v>
+        <v>20285</v>
       </c>
       <c r="C164" t="n">
-        <v>108.43</v>
+        <v>67.17</v>
       </c>
       <c r="D164" t="n">
-        <v>25295</v>
+        <v>23799</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>91.75</v>
+        <v>56.15</v>
       </c>
       <c r="B165" t="n">
-        <v>24985</v>
+        <v>21913</v>
       </c>
       <c r="C165" t="n">
-        <v>92.09999999999999</v>
+        <v>50.07</v>
       </c>
       <c r="D165" t="n">
-        <v>28116</v>
+        <v>18613</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>59.86</v>
+        <v>57.07</v>
       </c>
       <c r="B166" t="n">
-        <v>20916</v>
+        <v>21410</v>
       </c>
       <c r="C166" t="n">
-        <v>62.23</v>
+        <v>72.47</v>
       </c>
       <c r="D166" t="n">
-        <v>25821</v>
+        <v>16116</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>95.53</v>
+        <v>57.08</v>
       </c>
       <c r="B167" t="n">
-        <v>35605</v>
+        <v>19453</v>
       </c>
       <c r="C167" t="n">
-        <v>95.08</v>
+        <v>64.53</v>
       </c>
       <c r="D167" t="n">
-        <v>11203</v>
+        <v>27590</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>108.83</v>
+        <v>57.29</v>
       </c>
       <c r="B168" t="n">
-        <v>37081</v>
+        <v>21416</v>
       </c>
       <c r="C168" t="n">
-        <v>106.82</v>
+        <v>51.29</v>
       </c>
       <c r="D168" t="n">
-        <v>15866</v>
+        <v>29651</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119.28</v>
+        <v>57.83</v>
       </c>
       <c r="B169" t="n">
-        <v>22198</v>
+        <v>20988</v>
       </c>
       <c r="C169" t="n">
-        <v>123.31</v>
+        <v>62.2</v>
       </c>
       <c r="D169" t="n">
-        <v>17742</v>
+        <v>27141</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126.13</v>
+        <v>58.22</v>
       </c>
       <c r="B170" t="n">
-        <v>22069</v>
+        <v>20360</v>
       </c>
       <c r="C170" t="n">
-        <v>130.37</v>
+        <v>67.64</v>
       </c>
       <c r="D170" t="n">
-        <v>27037</v>
+        <v>22597</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>95.91</v>
+        <v>58.43</v>
       </c>
       <c r="B171" t="n">
-        <v>35646</v>
+        <v>21256</v>
       </c>
       <c r="C171" t="n">
-        <v>97.64</v>
+        <v>41.38</v>
       </c>
       <c r="D171" t="n">
-        <v>20120</v>
+        <v>10710</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>91.8</v>
+        <v>58.45</v>
       </c>
       <c r="B172" t="n">
-        <v>23131</v>
+        <v>19308</v>
       </c>
       <c r="C172" t="n">
-        <v>93.67</v>
+        <v>41.98</v>
       </c>
       <c r="D172" t="n">
-        <v>22455</v>
+        <v>14858</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>103.65</v>
+        <v>59.09</v>
       </c>
       <c r="B173" t="n">
-        <v>47376</v>
+        <v>21434</v>
       </c>
       <c r="C173" t="n">
-        <v>108.18</v>
+        <v>45.73</v>
       </c>
       <c r="D173" t="n">
-        <v>11168</v>
+        <v>23846</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>101.9</v>
+        <v>59.87</v>
       </c>
       <c r="B174" t="n">
-        <v>47203</v>
+        <v>22818</v>
       </c>
       <c r="C174" t="n">
-        <v>105.96</v>
+        <v>69.87</v>
       </c>
       <c r="D174" t="n">
-        <v>11484</v>
+        <v>10599</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>107.01</v>
+        <v>60.34</v>
       </c>
       <c r="B175" t="n">
-        <v>39322</v>
+        <v>22247</v>
       </c>
       <c r="C175" t="n">
-        <v>105.45</v>
+        <v>47.36</v>
       </c>
       <c r="D175" t="n">
-        <v>13883</v>
+        <v>26385</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>114.4</v>
+        <v>60.51</v>
       </c>
       <c r="B176" t="n">
-        <v>24324</v>
+        <v>21214</v>
       </c>
       <c r="C176" t="n">
-        <v>117.98</v>
+        <v>68.64</v>
       </c>
       <c r="D176" t="n">
-        <v>12839</v>
+        <v>21468</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>80</v>
+        <v>60.53</v>
       </c>
       <c r="B177" t="n">
-        <v>23987</v>
+        <v>20785</v>
       </c>
       <c r="C177" t="n">
-        <v>80.8</v>
+        <v>51.47</v>
       </c>
       <c r="D177" t="n">
-        <v>19423</v>
+        <v>13310</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>104.53</v>
+        <v>60.55</v>
       </c>
       <c r="B178" t="n">
-        <v>44479</v>
+        <v>21001</v>
       </c>
       <c r="C178" t="n">
-        <v>107.77</v>
+        <v>46.73</v>
       </c>
       <c r="D178" t="n">
-        <v>17784</v>
+        <v>11568</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>111.92</v>
+        <v>60.88</v>
       </c>
       <c r="B179" t="n">
-        <v>28854</v>
+        <v>23117</v>
       </c>
       <c r="C179" t="n">
-        <v>108.94</v>
+        <v>68.02</v>
       </c>
       <c r="D179" t="n">
-        <v>15198</v>
+        <v>28807</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>96.64</v>
+        <v>61.31</v>
       </c>
       <c r="B180" t="n">
-        <v>36543</v>
+        <v>21386</v>
       </c>
       <c r="C180" t="n">
-        <v>96.38</v>
+        <v>52.98</v>
       </c>
       <c r="D180" t="n">
-        <v>21550</v>
+        <v>23618</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>63.23</v>
+        <v>61.32</v>
       </c>
       <c r="B181" t="n">
-        <v>26403</v>
+        <v>19033</v>
       </c>
       <c r="C181" t="n">
-        <v>61.84</v>
+        <v>75.73</v>
       </c>
       <c r="D181" t="n">
-        <v>15859</v>
+        <v>14512</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>100.85</v>
+        <v>61.4</v>
       </c>
       <c r="B182" t="n">
-        <v>45606</v>
+        <v>22691</v>
       </c>
       <c r="C182" t="n">
-        <v>102.25</v>
+        <v>57.66</v>
       </c>
       <c r="D182" t="n">
-        <v>21757</v>
+        <v>14289</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>97.25</v>
+        <v>61.5</v>
       </c>
       <c r="B183" t="n">
-        <v>39675</v>
+        <v>20629</v>
       </c>
       <c r="C183" t="n">
-        <v>97.14</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="D183" t="n">
-        <v>16778</v>
+        <v>14823</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>104.46</v>
+        <v>61.6</v>
       </c>
       <c r="B184" t="n">
-        <v>48666</v>
+        <v>20206</v>
       </c>
       <c r="C184" t="n">
-        <v>108.32</v>
+        <v>55.77</v>
       </c>
       <c r="D184" t="n">
-        <v>25410</v>
+        <v>10929</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>104.63</v>
+        <v>61.83</v>
       </c>
       <c r="B185" t="n">
-        <v>46299</v>
+        <v>21678</v>
       </c>
       <c r="C185" t="n">
-        <v>108.88</v>
+        <v>58.3</v>
       </c>
       <c r="D185" t="n">
-        <v>16256</v>
+        <v>20622</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>99.06</v>
+        <v>61.84</v>
       </c>
       <c r="B186" t="n">
-        <v>42458</v>
+        <v>21332</v>
       </c>
       <c r="C186" t="n">
-        <v>102.02</v>
+        <v>75.17</v>
       </c>
       <c r="D186" t="n">
-        <v>19024</v>
+        <v>15957</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>82.28</v>
+        <v>62.36</v>
       </c>
       <c r="B187" t="n">
-        <v>21661</v>
+        <v>21546</v>
       </c>
       <c r="C187" t="n">
-        <v>83.75</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="D187" t="n">
-        <v>17215</v>
+        <v>21489</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>102.53</v>
+        <v>62.44</v>
       </c>
       <c r="B188" t="n">
-        <v>46751</v>
+        <v>20765</v>
       </c>
       <c r="C188" t="n">
-        <v>102.3</v>
+        <v>55.34</v>
       </c>
       <c r="D188" t="n">
-        <v>28121</v>
+        <v>16807</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>112.4</v>
+        <v>62.74</v>
       </c>
       <c r="B189" t="n">
-        <v>25088</v>
+        <v>20307</v>
       </c>
       <c r="C189" t="n">
-        <v>116.5</v>
+        <v>67.23</v>
       </c>
       <c r="D189" t="n">
-        <v>21384</v>
+        <v>22014</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>104.91</v>
+        <v>62.9</v>
       </c>
       <c r="B190" t="n">
-        <v>45627</v>
+        <v>21925</v>
       </c>
       <c r="C190" t="n">
-        <v>103.48</v>
+        <v>64.2</v>
       </c>
       <c r="D190" t="n">
-        <v>15937</v>
+        <v>13446</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>114.24</v>
+        <v>63.47</v>
       </c>
       <c r="B191" t="n">
-        <v>22973</v>
+        <v>21526</v>
       </c>
       <c r="C191" t="n">
-        <v>114.45</v>
+        <v>58.53</v>
       </c>
       <c r="D191" t="n">
-        <v>22528</v>
+        <v>19098</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>91.47</v>
+        <v>63.53</v>
       </c>
       <c r="B192" t="n">
-        <v>24620</v>
+        <v>19446</v>
       </c>
       <c r="C192" t="n">
-        <v>88.48</v>
+        <v>67.52</v>
       </c>
       <c r="D192" t="n">
-        <v>22661</v>
+        <v>29671</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>97.31999999999999</v>
+        <v>63.67</v>
       </c>
       <c r="B193" t="n">
-        <v>38939</v>
+        <v>20105</v>
       </c>
       <c r="C193" t="n">
-        <v>93.08</v>
+        <v>61.83</v>
       </c>
       <c r="D193" t="n">
-        <v>10034</v>
+        <v>29918</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>95.59999999999999</v>
+        <v>63.81</v>
       </c>
       <c r="B194" t="n">
-        <v>35925</v>
+        <v>19736</v>
       </c>
       <c r="C194" t="n">
-        <v>92.97</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="D194" t="n">
-        <v>22760</v>
+        <v>10382</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>112.61</v>
+        <v>63.82</v>
       </c>
       <c r="B195" t="n">
-        <v>24966</v>
+        <v>20092</v>
       </c>
       <c r="C195" t="n">
-        <v>112.56</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="D195" t="n">
-        <v>22951</v>
+        <v>28091</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>91.93000000000001</v>
+        <v>65.91</v>
       </c>
       <c r="B196" t="n">
-        <v>24890</v>
+        <v>20877</v>
       </c>
       <c r="C196" t="n">
-        <v>94.51000000000001</v>
+        <v>60.66</v>
       </c>
       <c r="D196" t="n">
-        <v>26403</v>
+        <v>10017</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>103.78</v>
+        <v>66.12</v>
       </c>
       <c r="B197" t="n">
-        <v>46864</v>
+        <v>21084</v>
       </c>
       <c r="C197" t="n">
-        <v>107.68</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D197" t="n">
-        <v>29506</v>
+        <v>22467</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>114.75</v>
+        <v>66.64</v>
       </c>
       <c r="B198" t="n">
-        <v>23442</v>
+        <v>22009</v>
       </c>
       <c r="C198" t="n">
-        <v>111.33</v>
+        <v>59.62</v>
       </c>
       <c r="D198" t="n">
-        <v>11611</v>
+        <v>27894</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>95.58</v>
+        <v>66.89</v>
       </c>
       <c r="B199" t="n">
-        <v>37053</v>
+        <v>20533</v>
       </c>
       <c r="C199" t="n">
-        <v>92.19</v>
+        <v>78.11</v>
       </c>
       <c r="D199" t="n">
-        <v>28557</v>
+        <v>18811</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>100.8</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="B200" t="n">
-        <v>43848</v>
+        <v>21073</v>
       </c>
       <c r="C200" t="n">
-        <v>100.5</v>
+        <v>56.09</v>
       </c>
       <c r="D200" t="n">
-        <v>25469</v>
+        <v>23568</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>105.13</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="B201" t="n">
-        <v>46334</v>
+        <v>19981</v>
       </c>
       <c r="C201" t="n">
-        <v>100.86</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="D201" t="n">
-        <v>15384</v>
+        <v>16048</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>98.37</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="B202" t="n">
-        <v>44820</v>
+        <v>19734</v>
       </c>
       <c r="C202" t="n">
-        <v>97.72</v>
+        <v>81.14</v>
       </c>
       <c r="D202" t="n">
-        <v>19675</v>
+        <v>12444</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>98.95</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="B203" t="n">
-        <v>41394</v>
+        <v>20793</v>
       </c>
       <c r="C203" t="n">
-        <v>95.48</v>
+        <v>79.42</v>
       </c>
       <c r="D203" t="n">
-        <v>19196</v>
+        <v>11241</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>101.42</v>
+        <v>67.86</v>
       </c>
       <c r="B204" t="n">
-        <v>44371</v>
+        <v>19694</v>
       </c>
       <c r="C204" t="n">
-        <v>99.81999999999999</v>
+        <v>62.91</v>
       </c>
       <c r="D204" t="n">
-        <v>16758</v>
+        <v>16131</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>112.98</v>
+        <v>68.25</v>
       </c>
       <c r="B205" t="n">
-        <v>26278</v>
+        <v>19437</v>
       </c>
       <c r="C205" t="n">
-        <v>116.64</v>
+        <v>56.9</v>
       </c>
       <c r="D205" t="n">
-        <v>18629</v>
+        <v>16303</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>100.72</v>
+        <v>68.5</v>
       </c>
       <c r="B206" t="n">
-        <v>45421</v>
+        <v>19604</v>
       </c>
       <c r="C206" t="n">
-        <v>99.06999999999999</v>
+        <v>79.08</v>
       </c>
       <c r="D206" t="n">
-        <v>10279</v>
+        <v>19410</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>100.01</v>
+        <v>68.52</v>
       </c>
       <c r="B207" t="n">
-        <v>44240</v>
+        <v>20983</v>
       </c>
       <c r="C207" t="n">
-        <v>100.62</v>
+        <v>77.41</v>
       </c>
       <c r="D207" t="n">
-        <v>22001</v>
+        <v>10442</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>143.06</v>
+        <v>69.44</v>
       </c>
       <c r="B208" t="n">
-        <v>24199</v>
+        <v>21473</v>
       </c>
       <c r="C208" t="n">
-        <v>142.12</v>
+        <v>56.19</v>
       </c>
       <c r="D208" t="n">
-        <v>20814</v>
+        <v>18495</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>176.74</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="B209" t="n">
-        <v>25194</v>
+        <v>20331</v>
       </c>
       <c r="C209" t="n">
-        <v>180</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="D209" t="n">
-        <v>28983</v>
+        <v>13811</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>100.48</v>
+        <v>70.11</v>
       </c>
       <c r="B210" t="n">
-        <v>45667</v>
+        <v>21385</v>
       </c>
       <c r="C210" t="n">
-        <v>98.18000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D210" t="n">
-        <v>19201</v>
+        <v>10641</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>105.58</v>
+        <v>70.55</v>
       </c>
       <c r="B211" t="n">
-        <v>44386</v>
+        <v>19324</v>
       </c>
       <c r="C211" t="n">
-        <v>106.64</v>
+        <v>73.8</v>
       </c>
       <c r="D211" t="n">
-        <v>11465</v>
+        <v>29148</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>114.9</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="B212" t="n">
-        <v>22886</v>
+        <v>20854</v>
       </c>
       <c r="C212" t="n">
-        <v>113.25</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="D212" t="n">
-        <v>21666</v>
+        <v>12492</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>106.17</v>
+        <v>70.95</v>
       </c>
       <c r="B213" t="n">
-        <v>43691</v>
+        <v>20745</v>
       </c>
       <c r="C213" t="n">
-        <v>106.59</v>
+        <v>59.22</v>
       </c>
       <c r="D213" t="n">
-        <v>25496</v>
+        <v>11707</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>110.56</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="B214" t="n">
-        <v>28915</v>
+        <v>20193</v>
       </c>
       <c r="C214" t="n">
-        <v>113.42</v>
+        <v>77.37</v>
       </c>
       <c r="D214" t="n">
-        <v>13993</v>
+        <v>25594</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>96.89</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="B215" t="n">
-        <v>40648</v>
+        <v>20221</v>
       </c>
       <c r="C215" t="n">
-        <v>99.95999999999999</v>
+        <v>68.33</v>
       </c>
       <c r="D215" t="n">
-        <v>20639</v>
+        <v>13125</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>103.04</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="B216" t="n">
-        <v>47484</v>
+        <v>21505</v>
       </c>
       <c r="C216" t="n">
-        <v>98.95999999999999</v>
+        <v>64.75</v>
       </c>
       <c r="D216" t="n">
-        <v>21478</v>
+        <v>16230</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>103.14</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="B217" t="n">
-        <v>47673</v>
+        <v>20972</v>
       </c>
       <c r="C217" t="n">
-        <v>105.53</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="D217" t="n">
-        <v>10706</v>
+        <v>17607</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>97.72</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="B218" t="n">
-        <v>44651</v>
+        <v>19341</v>
       </c>
       <c r="C218" t="n">
-        <v>99.7</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="D218" t="n">
-        <v>11578</v>
+        <v>18049</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>109.68</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="B219" t="n">
-        <v>33077</v>
+        <v>20123</v>
       </c>
       <c r="C219" t="n">
-        <v>112.93</v>
+        <v>79.16</v>
       </c>
       <c r="D219" t="n">
-        <v>20007</v>
+        <v>26034</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>110.47</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="B220" t="n">
-        <v>29505</v>
+        <v>21128</v>
       </c>
       <c r="C220" t="n">
-        <v>108.38</v>
+        <v>79.78</v>
       </c>
       <c r="D220" t="n">
-        <v>29344</v>
+        <v>25120</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>104</v>
+        <v>71.86</v>
       </c>
       <c r="B221" t="n">
-        <v>47897</v>
+        <v>20682</v>
       </c>
       <c r="C221" t="n">
-        <v>105.7</v>
+        <v>84.63</v>
       </c>
       <c r="D221" t="n">
-        <v>10583</v>
+        <v>10573</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>113.31</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="B222" t="n">
-        <v>23711</v>
+        <v>20804</v>
       </c>
       <c r="C222" t="n">
-        <v>118.05</v>
+        <v>90.84</v>
       </c>
       <c r="D222" t="n">
-        <v>11237</v>
+        <v>10244</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>21.24</v>
+        <v>72.09</v>
       </c>
       <c r="B223" t="n">
-        <v>24032</v>
+        <v>21791</v>
       </c>
       <c r="C223" t="n">
-        <v>21.1</v>
+        <v>81.23</v>
       </c>
       <c r="D223" t="n">
-        <v>26440</v>
+        <v>20540</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>72.08</v>
+        <v>72.69</v>
       </c>
       <c r="B224" t="n">
-        <v>23700</v>
+        <v>20016</v>
       </c>
       <c r="C224" t="n">
-        <v>70.40000000000001</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="D224" t="n">
-        <v>27967</v>
+        <v>23687</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>101.15</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="B225" t="n">
-        <v>46580</v>
+        <v>19981</v>
       </c>
       <c r="C225" t="n">
-        <v>101.33</v>
+        <v>88.19</v>
       </c>
       <c r="D225" t="n">
-        <v>27725</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>107.13</v>
+        <v>72.83</v>
       </c>
       <c r="B226" t="n">
-        <v>40049</v>
+        <v>21421</v>
       </c>
       <c r="C226" t="n">
-        <v>103.69</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="D226" t="n">
-        <v>14244</v>
+        <v>27506</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>108.93</v>
+        <v>73.28</v>
       </c>
       <c r="B227" t="n">
-        <v>34541</v>
+        <v>19166</v>
       </c>
       <c r="C227" t="n">
-        <v>106.99</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="D227" t="n">
-        <v>16616</v>
+        <v>27897</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>165.16</v>
+        <v>74.5</v>
       </c>
       <c r="B228" t="n">
-        <v>21558</v>
+        <v>19343</v>
       </c>
       <c r="C228" t="n">
-        <v>159.63</v>
+        <v>72.48</v>
       </c>
       <c r="D228" t="n">
-        <v>27554</v>
+        <v>27173</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>90.58</v>
+        <v>74.8</v>
       </c>
       <c r="B229" t="n">
-        <v>23948</v>
+        <v>20584</v>
       </c>
       <c r="C229" t="n">
-        <v>88.36</v>
+        <v>79.7</v>
       </c>
       <c r="D229" t="n">
-        <v>27800</v>
+        <v>22392</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>96.70999999999999</v>
+        <v>75.44</v>
       </c>
       <c r="B230" t="n">
-        <v>37781</v>
+        <v>20860</v>
       </c>
       <c r="C230" t="n">
-        <v>100.19</v>
+        <v>82.55</v>
       </c>
       <c r="D230" t="n">
-        <v>24274</v>
+        <v>19224</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>97.37</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="B231" t="n">
-        <v>39988</v>
+        <v>21874</v>
       </c>
       <c r="C231" t="n">
-        <v>94.16</v>
+        <v>56.06</v>
       </c>
       <c r="D231" t="n">
-        <v>16478</v>
+        <v>24837</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>94.25</v>
+        <v>76.02</v>
       </c>
       <c r="B232" t="n">
-        <v>33318</v>
+        <v>19734</v>
       </c>
       <c r="C232" t="n">
-        <v>94.09999999999999</v>
+        <v>64.67</v>
       </c>
       <c r="D232" t="n">
-        <v>22317</v>
+        <v>24979</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>100.43</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="B233" t="n">
-        <v>42309</v>
+        <v>20972</v>
       </c>
       <c r="C233" t="n">
-        <v>100.59</v>
+        <v>64.37</v>
       </c>
       <c r="D233" t="n">
-        <v>20249</v>
+        <v>25073</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>99.62</v>
+        <v>76.39</v>
       </c>
       <c r="B234" t="n">
-        <v>44509</v>
+        <v>20966</v>
       </c>
       <c r="C234" t="n">
-        <v>99.84</v>
+        <v>87.36</v>
       </c>
       <c r="D234" t="n">
-        <v>11957</v>
+        <v>29660</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>104.85</v>
+        <v>76.69</v>
       </c>
       <c r="B235" t="n">
-        <v>45140</v>
+        <v>20448</v>
       </c>
       <c r="C235" t="n">
-        <v>104.18</v>
+        <v>72.62</v>
       </c>
       <c r="D235" t="n">
-        <v>14093</v>
+        <v>15922</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>155.93</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="B236" t="n">
-        <v>24773</v>
+        <v>20660</v>
       </c>
       <c r="C236" t="n">
-        <v>154.08</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="D236" t="n">
-        <v>14190</v>
+        <v>18458</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>94.31999999999999</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="B237" t="n">
-        <v>32025</v>
+        <v>21689</v>
       </c>
       <c r="C237" t="n">
-        <v>95.3</v>
+        <v>90.2</v>
       </c>
       <c r="D237" t="n">
-        <v>10046</v>
+        <v>10510</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>108.44</v>
+        <v>78.23</v>
       </c>
       <c r="B238" t="n">
-        <v>38540</v>
+        <v>20162</v>
       </c>
       <c r="C238" t="n">
-        <v>106.9</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="D238" t="n">
-        <v>18510</v>
+        <v>12214</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>92.68000000000001</v>
+        <v>78.47</v>
       </c>
       <c r="B239" t="n">
-        <v>29543</v>
+        <v>20933</v>
       </c>
       <c r="C239" t="n">
-        <v>89.2</v>
+        <v>72.41</v>
       </c>
       <c r="D239" t="n">
-        <v>13336</v>
+        <v>19620</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>64.77</v>
+        <v>78.47</v>
       </c>
       <c r="B240" t="n">
-        <v>22225</v>
+        <v>20666</v>
       </c>
       <c r="C240" t="n">
-        <v>62.28</v>
+        <v>86.97</v>
       </c>
       <c r="D240" t="n">
-        <v>19235</v>
+        <v>28088</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>112.8</v>
+        <v>78.73</v>
       </c>
       <c r="B241" t="n">
-        <v>26396</v>
+        <v>19541</v>
       </c>
       <c r="C241" t="n">
-        <v>117.27</v>
+        <v>84.45</v>
       </c>
       <c r="D241" t="n">
-        <v>17405</v>
+        <v>15194</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>90.01000000000001</v>
+        <v>79.09</v>
       </c>
       <c r="B242" t="n">
-        <v>22807</v>
+        <v>20804</v>
       </c>
       <c r="C242" t="n">
-        <v>90.28</v>
+        <v>94.62</v>
       </c>
       <c r="D242" t="n">
-        <v>25377</v>
+        <v>23866</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>108.14</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="B243" t="n">
-        <v>38284</v>
+        <v>20206</v>
       </c>
       <c r="C243" t="n">
-        <v>108.43</v>
+        <v>61.53</v>
       </c>
       <c r="D243" t="n">
-        <v>17693</v>
+        <v>28379</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>113.47</v>
+        <v>79.56</v>
       </c>
       <c r="B244" t="n">
-        <v>23420</v>
+        <v>22205</v>
       </c>
       <c r="C244" t="n">
-        <v>109.42</v>
+        <v>101.48</v>
       </c>
       <c r="D244" t="n">
-        <v>19402</v>
+        <v>26453</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>11.42</v>
+        <v>79.88</v>
       </c>
       <c r="B245" t="n">
-        <v>23029</v>
+        <v>20075</v>
       </c>
       <c r="C245" t="n">
-        <v>11.7</v>
+        <v>77.75</v>
       </c>
       <c r="D245" t="n">
-        <v>18301</v>
+        <v>16608</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>163.73</v>
+        <v>80.47</v>
       </c>
       <c r="B246" t="n">
-        <v>23247</v>
+        <v>19292</v>
       </c>
       <c r="C246" t="n">
-        <v>168.13</v>
+        <v>77.91</v>
       </c>
       <c r="D246" t="n">
-        <v>13470</v>
+        <v>22157</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>111.57</v>
+        <v>80.86</v>
       </c>
       <c r="B247" t="n">
-        <v>30478</v>
+        <v>19866</v>
       </c>
       <c r="C247" t="n">
-        <v>113.89</v>
+        <v>80.38</v>
       </c>
       <c r="D247" t="n">
-        <v>17976</v>
+        <v>23549</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>93.04000000000001</v>
+        <v>81</v>
       </c>
       <c r="B248" t="n">
-        <v>27180</v>
+        <v>20594</v>
       </c>
       <c r="C248" t="n">
-        <v>89.44</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D248" t="n">
-        <v>16845</v>
+        <v>12471</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>107.63</v>
+        <v>81.05</v>
       </c>
       <c r="B249" t="n">
-        <v>39628</v>
+        <v>21215</v>
       </c>
       <c r="C249" t="n">
-        <v>107.44</v>
+        <v>77.16</v>
       </c>
       <c r="D249" t="n">
-        <v>11445</v>
+        <v>11525</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>97.42</v>
+        <v>81.08</v>
       </c>
       <c r="B250" t="n">
-        <v>39232</v>
+        <v>21101</v>
       </c>
       <c r="C250" t="n">
-        <v>100.14</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="D250" t="n">
-        <v>24287</v>
+        <v>17906</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>96.97</v>
+        <v>81.09</v>
       </c>
       <c r="B251" t="n">
-        <v>39186</v>
+        <v>20146</v>
       </c>
       <c r="C251" t="n">
-        <v>99.52</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="D251" t="n">
-        <v>24192</v>
+        <v>28677</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>95.65000000000001</v>
+        <v>82.08</v>
       </c>
       <c r="B252" t="n">
-        <v>35371</v>
+        <v>20923</v>
       </c>
       <c r="C252" t="n">
-        <v>94.33</v>
+        <v>98.20999999999999</v>
       </c>
       <c r="D252" t="n">
-        <v>13327</v>
+        <v>25339</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>74.31999999999999</v>
+        <v>82.13</v>
       </c>
       <c r="B253" t="n">
-        <v>26306</v>
+        <v>20274</v>
       </c>
       <c r="C253" t="n">
-        <v>77.87</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="D253" t="n">
-        <v>21512</v>
+        <v>28842</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>12.71</v>
+        <v>82.31</v>
       </c>
       <c r="B254" t="n">
-        <v>23672</v>
+        <v>20354</v>
       </c>
       <c r="C254" t="n">
-        <v>12.49</v>
+        <v>75.41</v>
       </c>
       <c r="D254" t="n">
-        <v>16987</v>
+        <v>19586</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>113.43</v>
+        <v>82.67</v>
       </c>
       <c r="B255" t="n">
-        <v>24011</v>
+        <v>21576</v>
       </c>
       <c r="C255" t="n">
-        <v>116.83</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="D255" t="n">
-        <v>28248</v>
+        <v>10227</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>96.16</v>
+        <v>83.66</v>
       </c>
       <c r="B256" t="n">
-        <v>35637</v>
+        <v>19956</v>
       </c>
       <c r="C256" t="n">
-        <v>98.20999999999999</v>
+        <v>93.41</v>
       </c>
       <c r="D256" t="n">
-        <v>23312</v>
+        <v>25178</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>109.48</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="B257" t="n">
-        <v>32484</v>
+        <v>20127</v>
       </c>
       <c r="C257" t="n">
-        <v>111.21</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="D257" t="n">
-        <v>20263</v>
+        <v>19772</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>124.7</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="B258" t="n">
-        <v>23947</v>
+        <v>21953</v>
       </c>
       <c r="C258" t="n">
-        <v>123.57</v>
+        <v>75.25</v>
       </c>
       <c r="D258" t="n">
-        <v>24725</v>
+        <v>19675</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>108.28</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="B259" t="n">
-        <v>38519</v>
+        <v>20647</v>
       </c>
       <c r="C259" t="n">
-        <v>106.54</v>
+        <v>90.8</v>
       </c>
       <c r="D259" t="n">
-        <v>17035</v>
+        <v>16834</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>92.34</v>
+        <v>85.75</v>
       </c>
       <c r="B260" t="n">
-        <v>25342</v>
+        <v>19890</v>
       </c>
       <c r="C260" t="n">
-        <v>95.41</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="D260" t="n">
-        <v>27694</v>
+        <v>17628</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>117.35</v>
+        <v>87.03</v>
       </c>
       <c r="B261" t="n">
-        <v>25781</v>
+        <v>20860</v>
       </c>
       <c r="C261" t="n">
-        <v>112.63</v>
+        <v>100.96</v>
       </c>
       <c r="D261" t="n">
-        <v>27553</v>
+        <v>27889</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>111.79</v>
+        <v>87.19</v>
       </c>
       <c r="B262" t="n">
-        <v>28570</v>
+        <v>20374</v>
       </c>
       <c r="C262" t="n">
-        <v>114.35</v>
+        <v>89.61</v>
       </c>
       <c r="D262" t="n">
-        <v>27941</v>
+        <v>29284</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>17.89</v>
+        <v>87.67</v>
       </c>
       <c r="B263" t="n">
-        <v>23517</v>
+        <v>21019</v>
       </c>
       <c r="C263" t="n">
-        <v>17.65</v>
+        <v>61.15</v>
       </c>
       <c r="D263" t="n">
-        <v>24022</v>
+        <v>21143</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>106.81</v>
+        <v>87.83</v>
       </c>
       <c r="B264" t="n">
-        <v>43650</v>
+        <v>19782</v>
       </c>
       <c r="C264" t="n">
-        <v>104.52</v>
+        <v>65.53</v>
       </c>
       <c r="D264" t="n">
-        <v>23562</v>
+        <v>13211</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>115.01</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="B265" t="n">
-        <v>21700</v>
+        <v>20143</v>
       </c>
       <c r="C265" t="n">
-        <v>111.75</v>
+        <v>76.53</v>
       </c>
       <c r="D265" t="n">
-        <v>21810</v>
+        <v>16927</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>112.77</v>
+        <v>88.78</v>
       </c>
       <c r="B266" t="n">
-        <v>25690</v>
+        <v>19818</v>
       </c>
       <c r="C266" t="n">
-        <v>114.78</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="D266" t="n">
-        <v>10564</v>
+        <v>29217</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>104.96</v>
+        <v>89</v>
       </c>
       <c r="B267" t="n">
-        <v>45675</v>
+        <v>20867</v>
       </c>
       <c r="C267" t="n">
-        <v>102.45</v>
+        <v>65.7</v>
       </c>
       <c r="D267" t="n">
-        <v>22513</v>
+        <v>29222</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>95.26000000000001</v>
+        <v>89.64</v>
       </c>
       <c r="B268" t="n">
-        <v>33409</v>
+        <v>20388</v>
       </c>
       <c r="C268" t="n">
-        <v>97.93000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D268" t="n">
-        <v>20506</v>
+        <v>21276</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>107.13</v>
+        <v>90.02</v>
       </c>
       <c r="B269" t="n">
-        <v>41541</v>
+        <v>20321</v>
       </c>
       <c r="C269" t="n">
-        <v>104.04</v>
+        <v>94.55</v>
       </c>
       <c r="D269" t="n">
-        <v>27441</v>
+        <v>15475</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>110.66</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="B270" t="n">
-        <v>29875</v>
+        <v>21441</v>
       </c>
       <c r="C270" t="n">
-        <v>106.36</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="D270" t="n">
-        <v>26601</v>
+        <v>11620</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>106.77</v>
+        <v>90.53</v>
       </c>
       <c r="B271" t="n">
-        <v>41240</v>
+        <v>21218</v>
       </c>
       <c r="C271" t="n">
-        <v>110.18</v>
+        <v>100.48</v>
       </c>
       <c r="D271" t="n">
-        <v>10731</v>
+        <v>18540</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>113.43</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="B272" t="n">
-        <v>22774</v>
+        <v>20841</v>
       </c>
       <c r="C272" t="n">
-        <v>115.58</v>
+        <v>114.91</v>
       </c>
       <c r="D272" t="n">
-        <v>28017</v>
+        <v>20332</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>90.58</v>
+        <v>91.8</v>
       </c>
       <c r="B273" t="n">
-        <v>24289</v>
+        <v>21386</v>
       </c>
       <c r="C273" t="n">
-        <v>86.84</v>
+        <v>90.42</v>
       </c>
       <c r="D273" t="n">
-        <v>25518</v>
+        <v>11065</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>112.1</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="B274" t="n">
-        <v>24275</v>
+        <v>22157</v>
       </c>
       <c r="C274" t="n">
-        <v>113.68</v>
+        <v>78.03</v>
       </c>
       <c r="D274" t="n">
-        <v>27192</v>
+        <v>20702</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>147.26</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="B275" t="n">
-        <v>24286</v>
+        <v>22923</v>
       </c>
       <c r="C275" t="n">
-        <v>147.99</v>
+        <v>78.27</v>
       </c>
       <c r="D275" t="n">
-        <v>17075</v>
+        <v>19806</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>102.23</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="B276" t="n">
-        <v>45282</v>
+        <v>22459</v>
       </c>
       <c r="C276" t="n">
-        <v>105.76</v>
+        <v>95.95</v>
       </c>
       <c r="D276" t="n">
-        <v>13554</v>
+        <v>14274</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>59.82</v>
+        <v>93.33</v>
       </c>
       <c r="B277" t="n">
-        <v>22419</v>
+        <v>23114</v>
       </c>
       <c r="C277" t="n">
-        <v>59.29</v>
+        <v>79.91</v>
       </c>
       <c r="D277" t="n">
-        <v>20302</v>
+        <v>16248</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>102.1</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="B278" t="n">
-        <v>46716</v>
+        <v>23713</v>
       </c>
       <c r="C278" t="n">
-        <v>103.5</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="D278" t="n">
-        <v>26789</v>
+        <v>17054</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>95.97</v>
+        <v>94.23</v>
       </c>
       <c r="B279" t="n">
-        <v>36667</v>
+        <v>24077</v>
       </c>
       <c r="C279" t="n">
-        <v>98.17</v>
+        <v>83.25</v>
       </c>
       <c r="D279" t="n">
-        <v>14020</v>
+        <v>14362</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>101.99</v>
+        <v>94.28</v>
       </c>
       <c r="B280" t="n">
-        <v>45989</v>
+        <v>24090</v>
       </c>
       <c r="C280" t="n">
-        <v>106.15</v>
+        <v>98.81</v>
       </c>
       <c r="D280" t="n">
-        <v>19663</v>
+        <v>21249</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>98.65000000000001</v>
+        <v>94.33</v>
       </c>
       <c r="B281" t="n">
-        <v>40185</v>
+        <v>24315</v>
       </c>
       <c r="C281" t="n">
-        <v>98.31999999999999</v>
+        <v>108.96</v>
       </c>
       <c r="D281" t="n">
-        <v>22741</v>
+        <v>15463</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>97.63</v>
+        <v>94.48</v>
       </c>
       <c r="B282" t="n">
-        <v>39901</v>
+        <v>24360</v>
       </c>
       <c r="C282" t="n">
-        <v>97</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="D282" t="n">
-        <v>16240</v>
+        <v>17776</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>86.23999999999999</v>
+        <v>94.77</v>
       </c>
       <c r="B283" t="n">
-        <v>24967</v>
+        <v>25022</v>
       </c>
       <c r="C283" t="n">
-        <v>84.67</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="D283" t="n">
-        <v>18721</v>
+        <v>29627</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>92.83</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="B284" t="n">
-        <v>27617</v>
+        <v>25593</v>
       </c>
       <c r="C284" t="n">
-        <v>91.63</v>
+        <v>71.8</v>
       </c>
       <c r="D284" t="n">
-        <v>15078</v>
+        <v>24302</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>101.84</v>
+        <v>95.45</v>
       </c>
       <c r="B285" t="n">
-        <v>45581</v>
+        <v>26752</v>
       </c>
       <c r="C285" t="n">
-        <v>99.04000000000001</v>
+        <v>95.67</v>
       </c>
       <c r="D285" t="n">
-        <v>21594</v>
+        <v>23622</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>108.96</v>
+        <v>95.62</v>
       </c>
       <c r="B286" t="n">
-        <v>35485</v>
+        <v>26062</v>
       </c>
       <c r="C286" t="n">
-        <v>107.9</v>
+        <v>113.94</v>
       </c>
       <c r="D286" t="n">
-        <v>16485</v>
+        <v>28142</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>101.98</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="B287" t="n">
-        <v>48002</v>
+        <v>26501</v>
       </c>
       <c r="C287" t="n">
-        <v>103.18</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="D287" t="n">
-        <v>15373</v>
+        <v>22298</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>113.41</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="B288" t="n">
-        <v>24723</v>
+        <v>28865</v>
       </c>
       <c r="C288" t="n">
-        <v>117.1</v>
+        <v>105.42</v>
       </c>
       <c r="D288" t="n">
-        <v>13742</v>
+        <v>14293</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>111.16</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="B289" t="n">
-        <v>27396</v>
+        <v>28756</v>
       </c>
       <c r="C289" t="n">
-        <v>112.38</v>
+        <v>119.94</v>
       </c>
       <c r="D289" t="n">
-        <v>13198</v>
+        <v>29783</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>109.54</v>
+        <v>98.31</v>
       </c>
       <c r="B290" t="n">
-        <v>34085</v>
+        <v>31498</v>
       </c>
       <c r="C290" t="n">
-        <v>110.94</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="D290" t="n">
-        <v>16422</v>
+        <v>23232</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>106.63</v>
+        <v>99.19</v>
       </c>
       <c r="B291" t="n">
-        <v>41069</v>
+        <v>32966</v>
       </c>
       <c r="C291" t="n">
-        <v>107.59</v>
+        <v>100.02</v>
       </c>
       <c r="D291" t="n">
-        <v>10704</v>
+        <v>22260</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>103.1</v>
+        <v>99.59</v>
       </c>
       <c r="B292" t="n">
-        <v>46034</v>
+        <v>34707</v>
       </c>
       <c r="C292" t="n">
-        <v>102.05</v>
+        <v>88.86</v>
       </c>
       <c r="D292" t="n">
-        <v>17622</v>
+        <v>11051</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>33.38</v>
+        <v>99.67</v>
       </c>
       <c r="B293" t="n">
-        <v>21606</v>
+        <v>34007</v>
       </c>
       <c r="C293" t="n">
-        <v>32.93</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D293" t="n">
-        <v>28454</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>107.22</v>
+        <v>100.05</v>
       </c>
       <c r="B294" t="n">
-        <v>40313</v>
+        <v>35882</v>
       </c>
       <c r="C294" t="n">
-        <v>110.85</v>
+        <v>124.49</v>
       </c>
       <c r="D294" t="n">
-        <v>29291</v>
+        <v>20851</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>105.49</v>
+        <v>100.11</v>
       </c>
       <c r="B295" t="n">
-        <v>45456</v>
+        <v>35864</v>
       </c>
       <c r="C295" t="n">
-        <v>108.38</v>
+        <v>73.19</v>
       </c>
       <c r="D295" t="n">
-        <v>17264</v>
+        <v>27534</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>22.04</v>
+        <v>101.31</v>
       </c>
       <c r="B296" t="n">
-        <v>23878</v>
+        <v>36608</v>
       </c>
       <c r="C296" t="n">
-        <v>21.09</v>
+        <v>79.19</v>
       </c>
       <c r="D296" t="n">
-        <v>25255</v>
+        <v>23726</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>114.55</v>
+        <v>102.09</v>
       </c>
       <c r="B297" t="n">
-        <v>23658</v>
+        <v>38311</v>
       </c>
       <c r="C297" t="n">
-        <v>112.77</v>
+        <v>92.67</v>
       </c>
       <c r="D297" t="n">
-        <v>20500</v>
+        <v>24298</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>97.33</v>
+        <v>102.17</v>
       </c>
       <c r="B298" t="n">
-        <v>39184</v>
+        <v>37189</v>
       </c>
       <c r="C298" t="n">
-        <v>100.45</v>
+        <v>101.63</v>
       </c>
       <c r="D298" t="n">
-        <v>24278</v>
+        <v>13373</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>91.41</v>
+        <v>102.47</v>
       </c>
       <c r="B299" t="n">
-        <v>24228</v>
+        <v>37959</v>
       </c>
       <c r="C299" t="n">
-        <v>92.73</v>
+        <v>122.66</v>
       </c>
       <c r="D299" t="n">
-        <v>25323</v>
+        <v>28570</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>136.32</v>
+        <v>102.65</v>
       </c>
       <c r="B300" t="n">
-        <v>23530</v>
+        <v>38211</v>
       </c>
       <c r="C300" t="n">
-        <v>136.91</v>
+        <v>107.28</v>
       </c>
       <c r="D300" t="n">
-        <v>11969</v>
+        <v>10596</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>93.89</v>
+        <v>102.93</v>
       </c>
       <c r="B301" t="n">
-        <v>30986</v>
+        <v>38367</v>
       </c>
       <c r="C301" t="n">
-        <v>92.79000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="D301" t="n">
-        <v>12623</v>
+        <v>29310</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>73.75</v>
+        <v>102.97</v>
       </c>
       <c r="B302" t="n">
-        <v>23864</v>
+        <v>38229</v>
       </c>
       <c r="C302" t="n">
-        <v>75.41</v>
+        <v>81.55</v>
       </c>
       <c r="D302" t="n">
-        <v>12076</v>
+        <v>12608</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>96.38</v>
+        <v>103.32</v>
       </c>
       <c r="B303" t="n">
-        <v>38565</v>
+        <v>38054</v>
       </c>
       <c r="C303" t="n">
-        <v>94.73999999999999</v>
+        <v>125.45</v>
       </c>
       <c r="D303" t="n">
-        <v>18174</v>
+        <v>19495</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>101.92</v>
+        <v>103.4</v>
       </c>
       <c r="B304" t="n">
-        <v>47673</v>
+        <v>38220</v>
       </c>
       <c r="C304" t="n">
-        <v>102.61</v>
+        <v>112.99</v>
       </c>
       <c r="D304" t="n">
-        <v>21448</v>
+        <v>18472</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>114.7</v>
+        <v>103.49</v>
       </c>
       <c r="B305" t="n">
-        <v>26214</v>
+        <v>37555</v>
       </c>
       <c r="C305" t="n">
-        <v>116.59</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="D305" t="n">
-        <v>10070</v>
+        <v>28960</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>111.64</v>
+        <v>103.68</v>
       </c>
       <c r="B306" t="n">
-        <v>26182</v>
+        <v>37917</v>
       </c>
       <c r="C306" t="n">
-        <v>114.3</v>
+        <v>108.78</v>
       </c>
       <c r="D306" t="n">
-        <v>14561</v>
+        <v>11689</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>90.56</v>
+        <v>104.77</v>
       </c>
       <c r="B307" t="n">
-        <v>24612</v>
+        <v>36895</v>
       </c>
       <c r="C307" t="n">
-        <v>94.01000000000001</v>
+        <v>111.47</v>
       </c>
       <c r="D307" t="n">
-        <v>27287</v>
+        <v>25966</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>107.99</v>
+        <v>104.8</v>
       </c>
       <c r="B308" t="n">
-        <v>39452</v>
+        <v>37060</v>
       </c>
       <c r="C308" t="n">
-        <v>109.72</v>
+        <v>85.11</v>
       </c>
       <c r="D308" t="n">
-        <v>18500</v>
+        <v>18356</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>47.93</v>
+        <v>105.1</v>
       </c>
       <c r="B309" t="n">
-        <v>21201</v>
+        <v>37077</v>
       </c>
       <c r="C309" t="n">
-        <v>49.95</v>
+        <v>127.25</v>
       </c>
       <c r="D309" t="n">
-        <v>26437</v>
+        <v>19969</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>126.84</v>
+        <v>105.2</v>
       </c>
       <c r="B310" t="n">
-        <v>22373</v>
+        <v>36284</v>
       </c>
       <c r="C310" t="n">
-        <v>121.91</v>
+        <v>90.48</v>
       </c>
       <c r="D310" t="n">
-        <v>22862</v>
+        <v>10071</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>99.94</v>
+        <v>106.64</v>
       </c>
       <c r="B311" t="n">
-        <v>44951</v>
+        <v>33682</v>
       </c>
       <c r="C311" t="n">
-        <v>101.9</v>
+        <v>104.03</v>
       </c>
       <c r="D311" t="n">
-        <v>15715</v>
+        <v>25494</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>75.69</v>
+        <v>106.75</v>
       </c>
       <c r="B312" t="n">
-        <v>24913</v>
+        <v>33897</v>
       </c>
       <c r="C312" t="n">
-        <v>75.62</v>
+        <v>110.36</v>
       </c>
       <c r="D312" t="n">
-        <v>10270</v>
+        <v>15151</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>107.24</v>
+        <v>106.79</v>
       </c>
       <c r="B313" t="n">
-        <v>42663</v>
+        <v>33561</v>
       </c>
       <c r="C313" t="n">
-        <v>108.63</v>
+        <v>95.98</v>
       </c>
       <c r="D313" t="n">
-        <v>13655</v>
+        <v>14628</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>113.59</v>
+        <v>107.1</v>
       </c>
       <c r="B314" t="n">
-        <v>25439</v>
+        <v>32455</v>
       </c>
       <c r="C314" t="n">
-        <v>113.26</v>
+        <v>103</v>
       </c>
       <c r="D314" t="n">
-        <v>22983</v>
+        <v>22560</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>113.44</v>
+        <v>108.57</v>
       </c>
       <c r="B315" t="n">
-        <v>27490</v>
+        <v>28729</v>
       </c>
       <c r="C315" t="n">
-        <v>112.57</v>
+        <v>126.91</v>
       </c>
       <c r="D315" t="n">
-        <v>15717</v>
+        <v>12456</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>40.82</v>
+        <v>109.5</v>
       </c>
       <c r="B316" t="n">
-        <v>25202</v>
+        <v>28303</v>
       </c>
       <c r="C316" t="n">
-        <v>39.11</v>
+        <v>110.55</v>
       </c>
       <c r="D316" t="n">
-        <v>19684</v>
+        <v>22327</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>96.45</v>
+        <v>109.79</v>
       </c>
       <c r="B317" t="n">
-        <v>37940</v>
+        <v>27273</v>
       </c>
       <c r="C317" t="n">
-        <v>92.53</v>
+        <v>122.59</v>
       </c>
       <c r="D317" t="n">
-        <v>16773</v>
+        <v>28074</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>107.51</v>
+        <v>109.99</v>
       </c>
       <c r="B318" t="n">
-        <v>40900</v>
+        <v>24217</v>
       </c>
       <c r="C318" t="n">
-        <v>104.92</v>
+        <v>126.15</v>
       </c>
       <c r="D318" t="n">
-        <v>11769</v>
+        <v>18689</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>103.85</v>
+        <v>110.15</v>
       </c>
       <c r="B319" t="n">
-        <v>45826</v>
+        <v>26486</v>
       </c>
       <c r="C319" t="n">
-        <v>105.52</v>
+        <v>114.1</v>
       </c>
       <c r="D319" t="n">
-        <v>19496</v>
+        <v>16381</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>112.02</v>
+        <v>110.66</v>
       </c>
       <c r="B320" t="n">
-        <v>28823</v>
+        <v>25256</v>
       </c>
       <c r="C320" t="n">
-        <v>116</v>
+        <v>137.9</v>
       </c>
       <c r="D320" t="n">
-        <v>21897</v>
+        <v>27237</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>106.77</v>
+        <v>110.93</v>
       </c>
       <c r="B321" t="n">
-        <v>44402</v>
+        <v>25362</v>
       </c>
       <c r="C321" t="n">
-        <v>107.28</v>
+        <v>116.67</v>
       </c>
       <c r="D321" t="n">
-        <v>15231</v>
+        <v>17465</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>91.23999999999999</v>
+        <v>111.25</v>
       </c>
       <c r="B322" t="n">
-        <v>24162</v>
+        <v>23674</v>
       </c>
       <c r="C322" t="n">
-        <v>89.33</v>
+        <v>137.83</v>
       </c>
       <c r="D322" t="n">
-        <v>12986</v>
+        <v>25082</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>101.33</v>
+        <v>111.74</v>
       </c>
       <c r="B323" t="n">
-        <v>47630</v>
+        <v>22521</v>
       </c>
       <c r="C323" t="n">
-        <v>100.68</v>
+        <v>86.38</v>
       </c>
       <c r="D323" t="n">
-        <v>23770</v>
+        <v>13018</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>94.48</v>
+        <v>112.28</v>
       </c>
       <c r="B324" t="n">
-        <v>32358</v>
+        <v>22364</v>
       </c>
       <c r="C324" t="n">
-        <v>92.78</v>
+        <v>113</v>
       </c>
       <c r="D324" t="n">
-        <v>28483</v>
+        <v>14430</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>95.58</v>
+        <v>112.7</v>
       </c>
       <c r="B325" t="n">
-        <v>35504</v>
+        <v>21673</v>
       </c>
       <c r="C325" t="n">
-        <v>92.92</v>
+        <v>118.35</v>
       </c>
       <c r="D325" t="n">
-        <v>26689</v>
+        <v>20956</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>90.23</v>
+        <v>112.82</v>
       </c>
       <c r="B326" t="n">
-        <v>25190</v>
+        <v>23747</v>
       </c>
       <c r="C326" t="n">
-        <v>94.12</v>
+        <v>114.58</v>
       </c>
       <c r="D326" t="n">
-        <v>19667</v>
+        <v>26241</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>100.4</v>
+        <v>112.85</v>
       </c>
       <c r="B327" t="n">
-        <v>44030</v>
+        <v>22318</v>
       </c>
       <c r="C327" t="n">
-        <v>102.73</v>
+        <v>125.32</v>
       </c>
       <c r="D327" t="n">
-        <v>27635</v>
+        <v>11515</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>90.87</v>
+        <v>113.05</v>
       </c>
       <c r="B328" t="n">
-        <v>22822</v>
+        <v>21594</v>
       </c>
       <c r="C328" t="n">
-        <v>90.59</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="D328" t="n">
-        <v>18097</v>
+        <v>15032</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>91.75</v>
+        <v>113.28</v>
       </c>
       <c r="B329" t="n">
-        <v>25408</v>
+        <v>21364</v>
       </c>
       <c r="C329" t="n">
-        <v>89.70999999999999</v>
+        <v>111.71</v>
       </c>
       <c r="D329" t="n">
-        <v>17589</v>
+        <v>18699</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>90.13</v>
+        <v>114.07</v>
       </c>
       <c r="B330" t="n">
-        <v>24117</v>
+        <v>20855</v>
       </c>
       <c r="C330" t="n">
-        <v>87.91</v>
+        <v>98.62</v>
       </c>
       <c r="D330" t="n">
-        <v>19105</v>
+        <v>29782</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>99.2</v>
+        <v>114.18</v>
       </c>
       <c r="B331" t="n">
-        <v>41831</v>
+        <v>20728</v>
       </c>
       <c r="C331" t="n">
-        <v>103.31</v>
+        <v>121.68</v>
       </c>
       <c r="D331" t="n">
-        <v>27585</v>
+        <v>26666</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>95.68000000000001</v>
+        <v>114.27</v>
       </c>
       <c r="B332" t="n">
-        <v>34476</v>
+        <v>22193</v>
       </c>
       <c r="C332" t="n">
-        <v>91.89</v>
+        <v>98.59</v>
       </c>
       <c r="D332" t="n">
-        <v>10920</v>
+        <v>21229</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>172.22</v>
+        <v>114.29</v>
       </c>
       <c r="B333" t="n">
-        <v>23276</v>
+        <v>19957</v>
       </c>
       <c r="C333" t="n">
-        <v>167.32</v>
+        <v>116.04</v>
       </c>
       <c r="D333" t="n">
-        <v>20471</v>
+        <v>17064</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>81.95</v>
+        <v>115.14</v>
       </c>
       <c r="B334" t="n">
-        <v>22358</v>
+        <v>19637</v>
       </c>
       <c r="C334" t="n">
-        <v>83.98</v>
+        <v>135.62</v>
       </c>
       <c r="D334" t="n">
-        <v>27989</v>
+        <v>13356</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>40.68</v>
+        <v>115.21</v>
       </c>
       <c r="B335" t="n">
-        <v>21111</v>
+        <v>21289</v>
       </c>
       <c r="C335" t="n">
-        <v>41.31</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="D335" t="n">
-        <v>25868</v>
+        <v>12313</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>99.86</v>
+        <v>115.31</v>
       </c>
       <c r="B336" t="n">
-        <v>46109</v>
+        <v>21465</v>
       </c>
       <c r="C336" t="n">
-        <v>103.89</v>
+        <v>104.15</v>
       </c>
       <c r="D336" t="n">
-        <v>20474</v>
+        <v>14905</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>92.17</v>
+        <v>115.32</v>
       </c>
       <c r="B337" t="n">
-        <v>28576</v>
+        <v>20074</v>
       </c>
       <c r="C337" t="n">
-        <v>92.2</v>
+        <v>101.86</v>
       </c>
       <c r="D337" t="n">
-        <v>24154</v>
+        <v>12520</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>97.5</v>
+        <v>115.51</v>
       </c>
       <c r="B338" t="n">
-        <v>38153</v>
+        <v>21960</v>
       </c>
       <c r="C338" t="n">
-        <v>97.87</v>
+        <v>122.17</v>
       </c>
       <c r="D338" t="n">
-        <v>25597</v>
+        <v>20798</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>96.55</v>
+        <v>115.63</v>
       </c>
       <c r="B339" t="n">
-        <v>34983</v>
+        <v>19636</v>
       </c>
       <c r="C339" t="n">
-        <v>99.2</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="D339" t="n">
-        <v>14127</v>
+        <v>13037</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>111.21</v>
+        <v>116.03</v>
       </c>
       <c r="B340" t="n">
-        <v>29138</v>
+        <v>20774</v>
       </c>
       <c r="C340" t="n">
-        <v>110.69</v>
+        <v>92.62</v>
       </c>
       <c r="D340" t="n">
-        <v>10701</v>
+        <v>23887</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>111.05</v>
+        <v>116.99</v>
       </c>
       <c r="B341" t="n">
-        <v>28521</v>
+        <v>21491</v>
       </c>
       <c r="C341" t="n">
-        <v>107.89</v>
+        <v>99.22</v>
       </c>
       <c r="D341" t="n">
-        <v>11217</v>
+        <v>26218</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>32.55</v>
+        <v>117.06</v>
       </c>
       <c r="B342" t="n">
-        <v>22905</v>
+        <v>18310</v>
       </c>
       <c r="C342" t="n">
-        <v>32.55</v>
+        <v>112.6</v>
       </c>
       <c r="D342" t="n">
-        <v>29237</v>
+        <v>28419</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>105.65</v>
+        <v>117.51</v>
       </c>
       <c r="B343" t="n">
-        <v>43579</v>
+        <v>19950</v>
       </c>
       <c r="C343" t="n">
-        <v>107.85</v>
+        <v>109.25</v>
       </c>
       <c r="D343" t="n">
-        <v>13989</v>
+        <v>15525</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>109.66</v>
+        <v>117.82</v>
       </c>
       <c r="B344" t="n">
-        <v>33820</v>
+        <v>19821</v>
       </c>
       <c r="C344" t="n">
-        <v>110.87</v>
+        <v>130.42</v>
       </c>
       <c r="D344" t="n">
-        <v>29020</v>
+        <v>13821</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>106.54</v>
+        <v>118.08</v>
       </c>
       <c r="B345" t="n">
-        <v>42040</v>
+        <v>18917</v>
       </c>
       <c r="C345" t="n">
-        <v>105.76</v>
+        <v>116.72</v>
       </c>
       <c r="D345" t="n">
-        <v>27254</v>
+        <v>24842</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>103.2</v>
+        <v>118.18</v>
       </c>
       <c r="B346" t="n">
-        <v>48938</v>
+        <v>20795</v>
       </c>
       <c r="C346" t="n">
-        <v>102.02</v>
+        <v>110.26</v>
       </c>
       <c r="D346" t="n">
-        <v>18712</v>
+        <v>13031</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>101.32</v>
+        <v>118.82</v>
       </c>
       <c r="B347" t="n">
-        <v>46556</v>
+        <v>18304</v>
       </c>
       <c r="C347" t="n">
-        <v>101.8</v>
+        <v>90.72</v>
       </c>
       <c r="D347" t="n">
-        <v>11355</v>
+        <v>24839</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>90.39</v>
+        <v>119.1</v>
       </c>
       <c r="B348" t="n">
-        <v>24238</v>
+        <v>19499</v>
       </c>
       <c r="C348" t="n">
-        <v>91.62</v>
+        <v>125.62</v>
       </c>
       <c r="D348" t="n">
-        <v>13049</v>
+        <v>22223</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>102.89</v>
+        <v>119.35</v>
       </c>
       <c r="B349" t="n">
-        <v>45586</v>
+        <v>19238</v>
       </c>
       <c r="C349" t="n">
-        <v>103.22</v>
+        <v>105.79</v>
       </c>
       <c r="D349" t="n">
-        <v>29042</v>
+        <v>13111</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>90.88</v>
+        <v>119.57</v>
       </c>
       <c r="B350" t="n">
-        <v>24145</v>
+        <v>18490</v>
       </c>
       <c r="C350" t="n">
-        <v>91.93000000000001</v>
+        <v>113.95</v>
       </c>
       <c r="D350" t="n">
-        <v>15791</v>
+        <v>10672</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>101.85</v>
+        <v>120.01</v>
       </c>
       <c r="B351" t="n">
-        <v>46507</v>
+        <v>18772</v>
       </c>
       <c r="C351" t="n">
-        <v>97.95</v>
+        <v>116.38</v>
       </c>
       <c r="D351" t="n">
-        <v>13447</v>
+        <v>27403</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>108.39</v>
+        <v>120.71</v>
       </c>
       <c r="B352" t="n">
-        <v>36833</v>
+        <v>18538</v>
       </c>
       <c r="C352" t="n">
-        <v>111.51</v>
+        <v>138.78</v>
       </c>
       <c r="D352" t="n">
-        <v>13761</v>
+        <v>10632</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>1.44</v>
+        <v>120.91</v>
       </c>
       <c r="B353" t="n">
-        <v>22791</v>
+        <v>19344</v>
       </c>
       <c r="C353" t="n">
-        <v>1.72</v>
+        <v>123</v>
       </c>
       <c r="D353" t="n">
-        <v>24836</v>
+        <v>18101</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>103.11</v>
+        <v>121.04</v>
       </c>
       <c r="B354" t="n">
-        <v>48235</v>
+        <v>21875</v>
       </c>
       <c r="C354" t="n">
-        <v>103.15</v>
+        <v>124.44</v>
       </c>
       <c r="D354" t="n">
-        <v>10467</v>
+        <v>29644</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>100.7</v>
+        <v>121.65</v>
       </c>
       <c r="B355" t="n">
-        <v>43276</v>
+        <v>20827</v>
       </c>
       <c r="C355" t="n">
-        <v>100.82</v>
+        <v>131.93</v>
       </c>
       <c r="D355" t="n">
-        <v>24435</v>
+        <v>26533</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>26.83</v>
+        <v>121.77</v>
       </c>
       <c r="B356" t="n">
-        <v>26780</v>
+        <v>19429</v>
       </c>
       <c r="C356" t="n">
-        <v>25.51</v>
+        <v>138.12</v>
       </c>
       <c r="D356" t="n">
-        <v>23468</v>
+        <v>27985</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>102.5</v>
+        <v>121.98</v>
       </c>
       <c r="B357" t="n">
-        <v>47974</v>
+        <v>20622</v>
       </c>
       <c r="C357" t="n">
-        <v>100.78</v>
+        <v>113.07</v>
       </c>
       <c r="D357" t="n">
-        <v>26490</v>
+        <v>16968</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>98.34</v>
+        <v>123.29</v>
       </c>
       <c r="B358" t="n">
-        <v>41502</v>
+        <v>20213</v>
       </c>
       <c r="C358" t="n">
-        <v>98.2</v>
+        <v>131.17</v>
       </c>
       <c r="D358" t="n">
-        <v>25063</v>
+        <v>18025</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>113.21</v>
+        <v>123.86</v>
       </c>
       <c r="B359" t="n">
-        <v>25027</v>
+        <v>20999</v>
       </c>
       <c r="C359" t="n">
-        <v>108.55</v>
+        <v>117.94</v>
       </c>
       <c r="D359" t="n">
-        <v>11011</v>
+        <v>23451</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>119.13</v>
+        <v>125.3</v>
       </c>
       <c r="B360" t="n">
-        <v>22881</v>
+        <v>19127</v>
       </c>
       <c r="C360" t="n">
-        <v>123.07</v>
+        <v>108.15</v>
       </c>
       <c r="D360" t="n">
-        <v>15948</v>
+        <v>14037</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>93.84999999999999</v>
+        <v>125.35</v>
       </c>
       <c r="B361" t="n">
-        <v>31063</v>
+        <v>19405</v>
       </c>
       <c r="C361" t="n">
-        <v>94.27</v>
+        <v>110.19</v>
       </c>
       <c r="D361" t="n">
-        <v>12044</v>
+        <v>15531</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>95.14</v>
+        <v>125.84</v>
       </c>
       <c r="B362" t="n">
-        <v>34430</v>
+        <v>20293</v>
       </c>
       <c r="C362" t="n">
-        <v>98.39</v>
+        <v>143.85</v>
       </c>
       <c r="D362" t="n">
-        <v>11445</v>
+        <v>17166</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>100.72</v>
+        <v>125.87</v>
       </c>
       <c r="B363" t="n">
-        <v>45190</v>
+        <v>20921</v>
       </c>
       <c r="C363" t="n">
-        <v>96</v>
+        <v>105.41</v>
       </c>
       <c r="D363" t="n">
-        <v>14280</v>
+        <v>24801</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>113.27</v>
+        <v>126.22</v>
       </c>
       <c r="B364" t="n">
-        <v>25233</v>
+        <v>18364</v>
       </c>
       <c r="C364" t="n">
-        <v>113.16</v>
+        <v>151.73</v>
       </c>
       <c r="D364" t="n">
-        <v>12422</v>
+        <v>26201</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>97.90000000000001</v>
+        <v>126.27</v>
       </c>
       <c r="B365" t="n">
-        <v>41010</v>
+        <v>19010</v>
       </c>
       <c r="C365" t="n">
-        <v>94.98</v>
+        <v>151.35</v>
       </c>
       <c r="D365" t="n">
-        <v>16762</v>
+        <v>16382</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>49.19</v>
+        <v>126.4</v>
       </c>
       <c r="B366" t="n">
-        <v>23963</v>
+        <v>18417</v>
       </c>
       <c r="C366" t="n">
-        <v>47.02</v>
+        <v>103.11</v>
       </c>
       <c r="D366" t="n">
-        <v>27247</v>
+        <v>23559</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>107.67</v>
+        <v>126.49</v>
       </c>
       <c r="B367" t="n">
-        <v>37570</v>
+        <v>19569</v>
       </c>
       <c r="C367" t="n">
-        <v>103.74</v>
+        <v>131.39</v>
       </c>
       <c r="D367" t="n">
-        <v>17207</v>
+        <v>19756</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>104.22</v>
+        <v>126.68</v>
       </c>
       <c r="B368" t="n">
-        <v>47220</v>
+        <v>20069</v>
       </c>
       <c r="C368" t="n">
-        <v>102.97</v>
+        <v>130.78</v>
       </c>
       <c r="D368" t="n">
-        <v>16879</v>
+        <v>20474</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>102.96</v>
+        <v>126.78</v>
       </c>
       <c r="B369" t="n">
-        <v>49019</v>
+        <v>20208</v>
       </c>
       <c r="C369" t="n">
-        <v>99.58</v>
+        <v>134.37</v>
       </c>
       <c r="D369" t="n">
-        <v>24452</v>
+        <v>18625</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>133</v>
+        <v>127.3</v>
       </c>
       <c r="B370" t="n">
-        <v>22794</v>
+        <v>17820</v>
       </c>
       <c r="C370" t="n">
-        <v>132.43</v>
+        <v>126.84</v>
       </c>
       <c r="D370" t="n">
-        <v>26612</v>
+        <v>15479</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>120.97</v>
+        <v>128.53</v>
       </c>
       <c r="B371" t="n">
-        <v>23958</v>
+        <v>20712</v>
       </c>
       <c r="C371" t="n">
-        <v>123.86</v>
+        <v>128.18</v>
       </c>
       <c r="D371" t="n">
-        <v>21522</v>
+        <v>24816</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>176.95</v>
+        <v>128.56</v>
       </c>
       <c r="B372" t="n">
-        <v>25753</v>
+        <v>19401</v>
       </c>
       <c r="C372" t="n">
-        <v>172.79</v>
+        <v>133.2</v>
       </c>
       <c r="D372" t="n">
-        <v>28831</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>105.26</v>
+        <v>128.64</v>
       </c>
       <c r="B373" t="n">
-        <v>45814</v>
+        <v>22151</v>
       </c>
       <c r="C373" t="n">
-        <v>104.98</v>
+        <v>120.34</v>
       </c>
       <c r="D373" t="n">
-        <v>24828</v>
+        <v>22318</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>91.8</v>
+        <v>129.15</v>
       </c>
       <c r="B374" t="n">
-        <v>24883</v>
+        <v>17818</v>
       </c>
       <c r="C374" t="n">
-        <v>91.90000000000001</v>
+        <v>124.15</v>
       </c>
       <c r="D374" t="n">
-        <v>19408</v>
+        <v>29261</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>100.58</v>
+        <v>130.22</v>
       </c>
       <c r="B375" t="n">
-        <v>46640</v>
+        <v>18366</v>
       </c>
       <c r="C375" t="n">
-        <v>102.06</v>
+        <v>130.37</v>
       </c>
       <c r="D375" t="n">
-        <v>24486</v>
+        <v>24972</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>134.51</v>
+        <v>130.29</v>
       </c>
       <c r="B376" t="n">
-        <v>21707</v>
+        <v>18249</v>
       </c>
       <c r="C376" t="n">
-        <v>130.14</v>
+        <v>134.95</v>
       </c>
       <c r="D376" t="n">
-        <v>11285</v>
+        <v>14125</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>92.11</v>
+        <v>130.9</v>
       </c>
       <c r="B377" t="n">
-        <v>26764</v>
+        <v>18194</v>
       </c>
       <c r="C377" t="n">
-        <v>94.02</v>
+        <v>121.77</v>
       </c>
       <c r="D377" t="n">
-        <v>28443</v>
+        <v>19807</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>109.97</v>
+        <v>131.06</v>
       </c>
       <c r="B378" t="n">
-        <v>30795</v>
+        <v>17735</v>
       </c>
       <c r="C378" t="n">
-        <v>106.28</v>
+        <v>103.44</v>
       </c>
       <c r="D378" t="n">
-        <v>29539</v>
+        <v>19615</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>110.28</v>
+        <v>131.4</v>
       </c>
       <c r="B379" t="n">
-        <v>33761</v>
+        <v>18550</v>
       </c>
       <c r="C379" t="n">
-        <v>108.45</v>
+        <v>107.67</v>
       </c>
       <c r="D379" t="n">
-        <v>24269</v>
+        <v>19004</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>100.16</v>
+        <v>132.16</v>
       </c>
       <c r="B380" t="n">
-        <v>44930</v>
+        <v>19086</v>
       </c>
       <c r="C380" t="n">
-        <v>96.09999999999999</v>
+        <v>142.52</v>
       </c>
       <c r="D380" t="n">
-        <v>11830</v>
+        <v>15705</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>99.93000000000001</v>
+        <v>132.39</v>
       </c>
       <c r="B381" t="n">
-        <v>44379</v>
+        <v>18531</v>
       </c>
       <c r="C381" t="n">
-        <v>98.39</v>
+        <v>114.11</v>
       </c>
       <c r="D381" t="n">
-        <v>19977</v>
+        <v>25888</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>106.8</v>
+        <v>132.54</v>
       </c>
       <c r="B382" t="n">
-        <v>43000</v>
+        <v>21699</v>
       </c>
       <c r="C382" t="n">
-        <v>107.9</v>
+        <v>122.53</v>
       </c>
       <c r="D382" t="n">
-        <v>28356</v>
+        <v>22253</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>98.31</v>
+        <v>132.59</v>
       </c>
       <c r="B383" t="n">
-        <v>41472</v>
+        <v>19038</v>
       </c>
       <c r="C383" t="n">
-        <v>97.58</v>
+        <v>140.4</v>
       </c>
       <c r="D383" t="n">
-        <v>19431</v>
+        <v>26287</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>94.64</v>
+        <v>132.76</v>
       </c>
       <c r="B384" t="n">
-        <v>33097</v>
+        <v>17978</v>
       </c>
       <c r="C384" t="n">
-        <v>91.61</v>
+        <v>134.53</v>
       </c>
       <c r="D384" t="n">
-        <v>28204</v>
+        <v>22663</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>164.52</v>
+        <v>133.4</v>
       </c>
       <c r="B385" t="n">
-        <v>23199</v>
+        <v>20551</v>
       </c>
       <c r="C385" t="n">
-        <v>168.43</v>
+        <v>159.96</v>
       </c>
       <c r="D385" t="n">
-        <v>26165</v>
+        <v>13864</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>51.91</v>
+        <v>133.41</v>
       </c>
       <c r="B386" t="n">
-        <v>24086</v>
+        <v>18225</v>
       </c>
       <c r="C386" t="n">
-        <v>50.83</v>
+        <v>141.2</v>
       </c>
       <c r="D386" t="n">
-        <v>17472</v>
+        <v>17055</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>97.16</v>
+        <v>133.44</v>
       </c>
       <c r="B387" t="n">
-        <v>37842</v>
+        <v>18228</v>
       </c>
       <c r="C387" t="n">
-        <v>95.88</v>
+        <v>130.28</v>
       </c>
       <c r="D387" t="n">
-        <v>29909</v>
+        <v>15795</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>119.78</v>
+        <v>133.45</v>
       </c>
       <c r="B388" t="n">
-        <v>24356</v>
+        <v>19373</v>
       </c>
       <c r="C388" t="n">
-        <v>116.85</v>
+        <v>123.15</v>
       </c>
       <c r="D388" t="n">
-        <v>16946</v>
+        <v>24920</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>111.2</v>
+        <v>133.54</v>
       </c>
       <c r="B389" t="n">
-        <v>27821</v>
+        <v>20109</v>
       </c>
       <c r="C389" t="n">
-        <v>111.88</v>
+        <v>148.73</v>
       </c>
       <c r="D389" t="n">
-        <v>11351</v>
+        <v>21955</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>48.83</v>
+        <v>133.57</v>
       </c>
       <c r="B390" t="n">
-        <v>24770</v>
+        <v>19241</v>
       </c>
       <c r="C390" t="n">
-        <v>47.35</v>
+        <v>125.4</v>
       </c>
       <c r="D390" t="n">
-        <v>24612</v>
+        <v>20826</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>90.22</v>
+        <v>134.04</v>
       </c>
       <c r="B391" t="n">
-        <v>27616</v>
+        <v>18997</v>
       </c>
       <c r="C391" t="n">
-        <v>87.45</v>
+        <v>136.6</v>
       </c>
       <c r="D391" t="n">
-        <v>18214</v>
+        <v>23889</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>93.29000000000001</v>
+        <v>134.44</v>
       </c>
       <c r="B392" t="n">
-        <v>30767</v>
+        <v>18603</v>
       </c>
       <c r="C392" t="n">
-        <v>96.90000000000001</v>
+        <v>116.97</v>
       </c>
       <c r="D392" t="n">
-        <v>17954</v>
+        <v>26008</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>90.44</v>
+        <v>135.57</v>
       </c>
       <c r="B393" t="n">
-        <v>25842</v>
+        <v>16476</v>
       </c>
       <c r="C393" t="n">
-        <v>87.44</v>
+        <v>116.05</v>
       </c>
       <c r="D393" t="n">
-        <v>20428</v>
+        <v>23091</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>95.3</v>
+        <v>135.59</v>
       </c>
       <c r="B394" t="n">
-        <v>34887</v>
+        <v>20812</v>
       </c>
       <c r="C394" t="n">
-        <v>97.97</v>
+        <v>130.6</v>
       </c>
       <c r="D394" t="n">
-        <v>28373</v>
+        <v>28297</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>161.08</v>
+        <v>136.98</v>
       </c>
       <c r="B395" t="n">
-        <v>23563</v>
+        <v>17086</v>
       </c>
       <c r="C395" t="n">
-        <v>163.96</v>
+        <v>125.63</v>
       </c>
       <c r="D395" t="n">
-        <v>10079</v>
+        <v>18983</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>112</v>
+        <v>137.15</v>
       </c>
       <c r="B396" t="n">
-        <v>27967</v>
+        <v>16578</v>
       </c>
       <c r="C396" t="n">
-        <v>112.92</v>
+        <v>149.4</v>
       </c>
       <c r="D396" t="n">
-        <v>19443</v>
+        <v>14434</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>91.38</v>
+        <v>137.58</v>
       </c>
       <c r="B397" t="n">
-        <v>25311</v>
+        <v>18492</v>
       </c>
       <c r="C397" t="n">
-        <v>88.93000000000001</v>
+        <v>127.11</v>
       </c>
       <c r="D397" t="n">
-        <v>14123</v>
+        <v>23864</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>106.04</v>
+        <v>138.88</v>
       </c>
       <c r="B398" t="n">
-        <v>43955</v>
+        <v>17903</v>
       </c>
       <c r="C398" t="n">
-        <v>108.77</v>
+        <v>133.93</v>
       </c>
       <c r="D398" t="n">
-        <v>24447</v>
+        <v>23443</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>178.75</v>
+        <v>139.22</v>
       </c>
       <c r="B399" t="n">
-        <v>23217</v>
+        <v>18266</v>
       </c>
       <c r="C399" t="n">
-        <v>180</v>
+        <v>114.5</v>
       </c>
       <c r="D399" t="n">
-        <v>26906</v>
+        <v>19041</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>106.07</v>
+        <v>139.61</v>
       </c>
       <c r="B400" t="n">
-        <v>46379</v>
+        <v>19515</v>
       </c>
       <c r="C400" t="n">
-        <v>106.29</v>
+        <v>129.07</v>
       </c>
       <c r="D400" t="n">
-        <v>28804</v>
+        <v>13391</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>102.9</v>
+        <v>139.61</v>
       </c>
       <c r="B401" t="n">
-        <v>43743</v>
+        <v>20471</v>
       </c>
       <c r="C401" t="n">
-        <v>103.84</v>
+        <v>154.73</v>
       </c>
       <c r="D401" t="n">
-        <v>18731</v>
+        <v>13757</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>109.37</v>
+        <v>139.73</v>
       </c>
       <c r="B402" t="n">
-        <v>33902</v>
+        <v>18208</v>
       </c>
       <c r="C402" t="n">
-        <v>112.28</v>
+        <v>132.62</v>
       </c>
       <c r="D402" t="n">
-        <v>29945</v>
+        <v>26006</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>95.14</v>
+        <v>140.18</v>
       </c>
       <c r="B403" t="n">
-        <v>34549</v>
+        <v>17206</v>
       </c>
       <c r="C403" t="n">
-        <v>98.95</v>
+        <v>177.25</v>
       </c>
       <c r="D403" t="n">
-        <v>28043</v>
+        <v>13660</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>107.12</v>
+        <v>141.03</v>
       </c>
       <c r="B404" t="n">
-        <v>41753</v>
+        <v>18934</v>
       </c>
       <c r="C404" t="n">
-        <v>108.8</v>
+        <v>134.43</v>
       </c>
       <c r="D404" t="n">
-        <v>23337</v>
+        <v>15806</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>110.57</v>
+        <v>141.43</v>
       </c>
       <c r="B405" t="n">
-        <v>31106</v>
+        <v>19755</v>
       </c>
       <c r="C405" t="n">
-        <v>110.08</v>
+        <v>154.12</v>
       </c>
       <c r="D405" t="n">
-        <v>12548</v>
+        <v>21143</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>106.87</v>
+        <v>141.67</v>
       </c>
       <c r="B406" t="n">
-        <v>40212</v>
+        <v>17821</v>
       </c>
       <c r="C406" t="n">
-        <v>110.52</v>
+        <v>138.48</v>
       </c>
       <c r="D406" t="n">
-        <v>16773</v>
+        <v>15788</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>94.14</v>
+        <v>142.03</v>
       </c>
       <c r="B407" t="n">
-        <v>29787</v>
+        <v>20368</v>
       </c>
       <c r="C407" t="n">
-        <v>98.58</v>
+        <v>163.25</v>
       </c>
       <c r="D407" t="n">
-        <v>16301</v>
+        <v>13826</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>92.02</v>
+        <v>142.49</v>
       </c>
       <c r="B408" t="n">
-        <v>27332</v>
+        <v>19122</v>
       </c>
       <c r="C408" t="n">
-        <v>95.58</v>
+        <v>134.98</v>
       </c>
       <c r="D408" t="n">
-        <v>24688</v>
+        <v>19234</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>94.90000000000001</v>
+        <v>143.88</v>
       </c>
       <c r="B409" t="n">
-        <v>32476</v>
+        <v>21264</v>
       </c>
       <c r="C409" t="n">
-        <v>93.90000000000001</v>
+        <v>140.07</v>
       </c>
       <c r="D409" t="n">
-        <v>19090</v>
+        <v>28212</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>108.71</v>
+        <v>143.96</v>
       </c>
       <c r="B410" t="n">
-        <v>39185</v>
+        <v>19443</v>
       </c>
       <c r="C410" t="n">
-        <v>110.67</v>
+        <v>129.31</v>
       </c>
       <c r="D410" t="n">
-        <v>14948</v>
+        <v>24675</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>151.74</v>
+        <v>144.19</v>
       </c>
       <c r="B411" t="n">
-        <v>24554</v>
+        <v>17187</v>
       </c>
       <c r="C411" t="n">
-        <v>148.93</v>
+        <v>167.89</v>
       </c>
       <c r="D411" t="n">
-        <v>10908</v>
+        <v>29476</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>113.98</v>
+        <v>144.25</v>
       </c>
       <c r="B412" t="n">
-        <v>23849</v>
+        <v>22000</v>
       </c>
       <c r="C412" t="n">
-        <v>119.34</v>
+        <v>146.98</v>
       </c>
       <c r="D412" t="n">
-        <v>18509</v>
+        <v>16541</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>112.02</v>
+        <v>144.71</v>
       </c>
       <c r="B413" t="n">
-        <v>25745</v>
+        <v>21730</v>
       </c>
       <c r="C413" t="n">
-        <v>111.09</v>
+        <v>169.07</v>
       </c>
       <c r="D413" t="n">
-        <v>21158</v>
+        <v>29952</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>113.79</v>
+        <v>144.72</v>
       </c>
       <c r="B414" t="n">
-        <v>25584</v>
+        <v>20160</v>
       </c>
       <c r="C414" t="n">
-        <v>112.39</v>
+        <v>173.59</v>
       </c>
       <c r="D414" t="n">
-        <v>26543</v>
+        <v>14931</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>101.41</v>
+        <v>145.81</v>
       </c>
       <c r="B415" t="n">
-        <v>44799</v>
+        <v>21260</v>
       </c>
       <c r="C415" t="n">
-        <v>101.13</v>
+        <v>115.72</v>
       </c>
       <c r="D415" t="n">
-        <v>18952</v>
+        <v>16262</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>114.08</v>
+        <v>146.14</v>
       </c>
       <c r="B416" t="n">
-        <v>23976</v>
+        <v>20906</v>
       </c>
       <c r="C416" t="n">
-        <v>110.42</v>
+        <v>171.99</v>
       </c>
       <c r="D416" t="n">
-        <v>25972</v>
+        <v>11471</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>107.33</v>
+        <v>146.41</v>
       </c>
       <c r="B417" t="n">
-        <v>40431</v>
+        <v>18003</v>
       </c>
       <c r="C417" t="n">
-        <v>107.46</v>
+        <v>160.49</v>
       </c>
       <c r="D417" t="n">
-        <v>16910</v>
+        <v>16025</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>33.41</v>
+        <v>146.91</v>
       </c>
       <c r="B418" t="n">
-        <v>25006</v>
+        <v>23395</v>
       </c>
       <c r="C418" t="n">
-        <v>33.45</v>
+        <v>130</v>
       </c>
       <c r="D418" t="n">
-        <v>26887</v>
+        <v>23074</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>101.22</v>
+        <v>147.37</v>
       </c>
       <c r="B419" t="n">
-        <v>46091</v>
+        <v>21951</v>
       </c>
       <c r="C419" t="n">
-        <v>102.56</v>
+        <v>149.3</v>
       </c>
       <c r="D419" t="n">
-        <v>26738</v>
+        <v>24995</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>168.19</v>
+        <v>147.89</v>
       </c>
       <c r="B420" t="n">
-        <v>23101</v>
+        <v>20702</v>
       </c>
       <c r="C420" t="n">
-        <v>173.71</v>
+        <v>122.87</v>
       </c>
       <c r="D420" t="n">
-        <v>17522</v>
+        <v>24088</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>12.74</v>
+        <v>147.95</v>
       </c>
       <c r="B421" t="n">
-        <v>25167</v>
+        <v>22293</v>
       </c>
       <c r="C421" t="n">
-        <v>12.88</v>
+        <v>111.93</v>
       </c>
       <c r="D421" t="n">
-        <v>10752</v>
+        <v>23222</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>100.66</v>
+        <v>147.99</v>
       </c>
       <c r="B422" t="n">
-        <v>42904</v>
+        <v>22320</v>
       </c>
       <c r="C422" t="n">
-        <v>102.75</v>
+        <v>165.13</v>
       </c>
       <c r="D422" t="n">
-        <v>28316</v>
+        <v>10547</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>102.02</v>
+        <v>148.31</v>
       </c>
       <c r="B423" t="n">
-        <v>49921</v>
+        <v>23660</v>
       </c>
       <c r="C423" t="n">
-        <v>100.84</v>
+        <v>162.28</v>
       </c>
       <c r="D423" t="n">
-        <v>27964</v>
+        <v>10063</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>95.88</v>
+        <v>148.9</v>
       </c>
       <c r="B424" t="n">
-        <v>35515</v>
+        <v>20099</v>
       </c>
       <c r="C424" t="n">
-        <v>93.7</v>
+        <v>164.57</v>
       </c>
       <c r="D424" t="n">
-        <v>14557</v>
+        <v>26722</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>97.05</v>
+        <v>149.3</v>
       </c>
       <c r="B425" t="n">
-        <v>37432</v>
+        <v>25703</v>
       </c>
       <c r="C425" t="n">
-        <v>94.84999999999999</v>
+        <v>179.71</v>
       </c>
       <c r="D425" t="n">
-        <v>20483</v>
+        <v>13661</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>96.12</v>
+        <v>149.43</v>
       </c>
       <c r="B426" t="n">
-        <v>37255</v>
+        <v>23014</v>
       </c>
       <c r="C426" t="n">
-        <v>98.06999999999999</v>
+        <v>119.55</v>
       </c>
       <c r="D426" t="n">
-        <v>20144</v>
+        <v>14401</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>126.55</v>
+        <v>149.99</v>
       </c>
       <c r="B427" t="n">
-        <v>22361</v>
+        <v>23645</v>
       </c>
       <c r="C427" t="n">
-        <v>123.18</v>
+        <v>155.86</v>
       </c>
       <c r="D427" t="n">
-        <v>19746</v>
+        <v>19653</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>112.45</v>
+        <v>150.08</v>
       </c>
       <c r="B428" t="n">
-        <v>27499</v>
+        <v>24398</v>
       </c>
       <c r="C428" t="n">
-        <v>108.84</v>
+        <v>140.02</v>
       </c>
       <c r="D428" t="n">
-        <v>13440</v>
+        <v>14598</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>108.17</v>
+        <v>150.13</v>
       </c>
       <c r="B429" t="n">
-        <v>40022</v>
+        <v>22820</v>
       </c>
       <c r="C429" t="n">
-        <v>110.54</v>
+        <v>138.11</v>
       </c>
       <c r="D429" t="n">
-        <v>13917</v>
+        <v>18684</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>114.01</v>
+        <v>150.16</v>
       </c>
       <c r="B430" t="n">
-        <v>22954</v>
+        <v>22159</v>
       </c>
       <c r="C430" t="n">
-        <v>111.34</v>
+        <v>154.62</v>
       </c>
       <c r="D430" t="n">
-        <v>22784</v>
+        <v>24600</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>94.98999999999999</v>
+        <v>150.31</v>
       </c>
       <c r="B431" t="n">
-        <v>34974</v>
+        <v>23985</v>
       </c>
       <c r="C431" t="n">
-        <v>94.98999999999999</v>
+        <v>142.02</v>
       </c>
       <c r="D431" t="n">
-        <v>24166</v>
+        <v>26836</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>106.91</v>
+        <v>150.35</v>
       </c>
       <c r="B432" t="n">
-        <v>41546</v>
+        <v>22589</v>
       </c>
       <c r="C432" t="n">
-        <v>102.59</v>
+        <v>168.82</v>
       </c>
       <c r="D432" t="n">
-        <v>22183</v>
+        <v>11780</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>113.01</v>
+        <v>150.61</v>
       </c>
       <c r="B433" t="n">
-        <v>25016</v>
+        <v>21712</v>
       </c>
       <c r="C433" t="n">
-        <v>111.91</v>
+        <v>124.81</v>
       </c>
       <c r="D433" t="n">
-        <v>14419</v>
+        <v>13247</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>102.83</v>
+        <v>151.04</v>
       </c>
       <c r="B434" t="n">
-        <v>46924</v>
+        <v>24073</v>
       </c>
       <c r="C434" t="n">
-        <v>102.48</v>
+        <v>170.64</v>
       </c>
       <c r="D434" t="n">
-        <v>26474</v>
+        <v>18964</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>22.64</v>
+        <v>151.3</v>
       </c>
       <c r="B435" t="n">
-        <v>22327</v>
+        <v>23956</v>
       </c>
       <c r="C435" t="n">
-        <v>23.43</v>
+        <v>160.7</v>
       </c>
       <c r="D435" t="n">
-        <v>23917</v>
+        <v>16004</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>98.61</v>
+        <v>151.43</v>
       </c>
       <c r="B436" t="n">
-        <v>41467</v>
+        <v>25617</v>
       </c>
       <c r="C436" t="n">
-        <v>101.4</v>
+        <v>143.12</v>
       </c>
       <c r="D436" t="n">
-        <v>23824</v>
+        <v>16479</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>102.84</v>
+        <v>151.92</v>
       </c>
       <c r="B437" t="n">
-        <v>46338</v>
+        <v>24935</v>
       </c>
       <c r="C437" t="n">
-        <v>99.26000000000001</v>
+        <v>171.55</v>
       </c>
       <c r="D437" t="n">
-        <v>25732</v>
+        <v>14105</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>107.49</v>
+        <v>151.99</v>
       </c>
       <c r="B438" t="n">
-        <v>39258</v>
+        <v>23688</v>
       </c>
       <c r="C438" t="n">
-        <v>108.04</v>
+        <v>138.52</v>
       </c>
       <c r="D438" t="n">
-        <v>28134</v>
+        <v>17692</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>94.98</v>
+        <v>152.11</v>
       </c>
       <c r="B439" t="n">
-        <v>30629</v>
+        <v>25924</v>
       </c>
       <c r="C439" t="n">
-        <v>93.02</v>
+        <v>159.58</v>
       </c>
       <c r="D439" t="n">
-        <v>13181</v>
+        <v>18611</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>110.6</v>
+        <v>152.43</v>
       </c>
       <c r="B440" t="n">
-        <v>33636</v>
+        <v>24209</v>
       </c>
       <c r="C440" t="n">
-        <v>108.81</v>
+        <v>150.37</v>
       </c>
       <c r="D440" t="n">
-        <v>13428</v>
+        <v>13464</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>152.65</v>
+        <v>153.4</v>
       </c>
       <c r="B441" t="n">
-        <v>23111</v>
+        <v>24160</v>
       </c>
       <c r="C441" t="n">
-        <v>157.05</v>
+        <v>135.54</v>
       </c>
       <c r="D441" t="n">
-        <v>16255</v>
+        <v>13563</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>104.26</v>
+        <v>154.05</v>
       </c>
       <c r="B442" t="n">
-        <v>43970</v>
+        <v>27594</v>
       </c>
       <c r="C442" t="n">
-        <v>106.5</v>
+        <v>152.16</v>
       </c>
       <c r="D442" t="n">
-        <v>18595</v>
+        <v>11201</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>113.29</v>
+        <v>155.57</v>
       </c>
       <c r="B443" t="n">
-        <v>22954</v>
+        <v>27827</v>
       </c>
       <c r="C443" t="n">
-        <v>111.76</v>
+        <v>138.14</v>
       </c>
       <c r="D443" t="n">
-        <v>23652</v>
+        <v>23543</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>101.9</v>
+        <v>155.65</v>
       </c>
       <c r="B444" t="n">
-        <v>48386</v>
+        <v>30498</v>
       </c>
       <c r="C444" t="n">
-        <v>98.43000000000001</v>
+        <v>152.99</v>
       </c>
       <c r="D444" t="n">
-        <v>26528</v>
+        <v>12732</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>93.23999999999999</v>
+        <v>155.7</v>
       </c>
       <c r="B445" t="n">
-        <v>29473</v>
+        <v>28283</v>
       </c>
       <c r="C445" t="n">
-        <v>96.52</v>
+        <v>161.83</v>
       </c>
       <c r="D445" t="n">
-        <v>12636</v>
+        <v>18397</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>92.25</v>
+        <v>156.58</v>
       </c>
       <c r="B446" t="n">
-        <v>27351</v>
+        <v>29719</v>
       </c>
       <c r="C446" t="n">
-        <v>90.18000000000001</v>
+        <v>131.95</v>
       </c>
       <c r="D446" t="n">
-        <v>26768</v>
+        <v>26074</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>103.79</v>
+        <v>156.82</v>
       </c>
       <c r="B447" t="n">
-        <v>46382</v>
+        <v>28559</v>
       </c>
       <c r="C447" t="n">
-        <v>100.97</v>
+        <v>153.32</v>
       </c>
       <c r="D447" t="n">
-        <v>10211</v>
+        <v>26622</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>95.08</v>
+        <v>156.84</v>
       </c>
       <c r="B448" t="n">
-        <v>34236</v>
+        <v>27007</v>
       </c>
       <c r="C448" t="n">
-        <v>92.95</v>
+        <v>148.94</v>
       </c>
       <c r="D448" t="n">
-        <v>26993</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>97.08</v>
+        <v>158.16</v>
       </c>
       <c r="B449" t="n">
-        <v>38029</v>
+        <v>26625</v>
       </c>
       <c r="C449" t="n">
-        <v>100.1</v>
+        <v>156.24</v>
       </c>
       <c r="D449" t="n">
-        <v>11737</v>
+        <v>19604</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>109.78</v>
+        <v>158.44</v>
       </c>
       <c r="B450" t="n">
-        <v>33043</v>
+        <v>28499</v>
       </c>
       <c r="C450" t="n">
-        <v>110.4</v>
+        <v>180</v>
       </c>
       <c r="D450" t="n">
-        <v>22582</v>
+        <v>18298</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>68.7</v>
+        <v>158.69</v>
       </c>
       <c r="B451" t="n">
-        <v>23653</v>
+        <v>29933</v>
       </c>
       <c r="C451" t="n">
-        <v>66.33</v>
+        <v>150.1</v>
       </c>
       <c r="D451" t="n">
-        <v>27505</v>
+        <v>15521</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>98.98999999999999</v>
+        <v>159.64</v>
       </c>
       <c r="B452" t="n">
-        <v>41308</v>
+        <v>31467</v>
       </c>
       <c r="C452" t="n">
-        <v>96.90000000000001</v>
+        <v>142.61</v>
       </c>
       <c r="D452" t="n">
-        <v>22966</v>
+        <v>15452</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>95.72</v>
+        <v>159.84</v>
       </c>
       <c r="B453" t="n">
-        <v>34305</v>
+        <v>28763</v>
       </c>
       <c r="C453" t="n">
-        <v>94.62</v>
+        <v>135.85</v>
       </c>
       <c r="D453" t="n">
-        <v>26044</v>
+        <v>17327</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>162.69</v>
+        <v>160.15</v>
       </c>
       <c r="B454" t="n">
-        <v>23547</v>
+        <v>30456</v>
       </c>
       <c r="C454" t="n">
-        <v>158.39</v>
+        <v>150.15</v>
       </c>
       <c r="D454" t="n">
-        <v>11689</v>
+        <v>10539</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>100.77</v>
+        <v>160.34</v>
       </c>
       <c r="B455" t="n">
-        <v>46169</v>
+        <v>29802</v>
       </c>
       <c r="C455" t="n">
-        <v>105.2</v>
+        <v>150.35</v>
       </c>
       <c r="D455" t="n">
-        <v>11454</v>
+        <v>12569</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>95.61</v>
+        <v>160.39</v>
       </c>
       <c r="B456" t="n">
-        <v>33965</v>
+        <v>31363</v>
       </c>
       <c r="C456" t="n">
-        <v>95.88</v>
+        <v>180</v>
       </c>
       <c r="D456" t="n">
-        <v>18675</v>
+        <v>17279</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>100.46</v>
+        <v>160.56</v>
       </c>
       <c r="B457" t="n">
-        <v>44228</v>
+        <v>28722</v>
       </c>
       <c r="C457" t="n">
-        <v>101.43</v>
+        <v>136.19</v>
       </c>
       <c r="D457" t="n">
-        <v>15827</v>
+        <v>17927</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>114.69</v>
+        <v>161.33</v>
       </c>
       <c r="B458" t="n">
-        <v>23815</v>
+        <v>29049</v>
       </c>
       <c r="C458" t="n">
-        <v>118.97</v>
+        <v>180</v>
       </c>
       <c r="D458" t="n">
-        <v>23561</v>
+        <v>16214</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>105.59</v>
+        <v>161.66</v>
       </c>
       <c r="B459" t="n">
-        <v>44133</v>
+        <v>32048</v>
       </c>
       <c r="C459" t="n">
-        <v>102.01</v>
+        <v>156.3</v>
       </c>
       <c r="D459" t="n">
-        <v>21552</v>
+        <v>24975</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>107.25</v>
+        <v>162.72</v>
       </c>
       <c r="B460" t="n">
-        <v>40790</v>
+        <v>28921</v>
       </c>
       <c r="C460" t="n">
-        <v>105.76</v>
+        <v>180</v>
       </c>
       <c r="D460" t="n">
-        <v>18941</v>
+        <v>15436</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>103.91</v>
+        <v>162.77</v>
       </c>
       <c r="B461" t="n">
-        <v>48057</v>
+        <v>29084</v>
       </c>
       <c r="C461" t="n">
-        <v>104.72</v>
+        <v>180</v>
       </c>
       <c r="D461" t="n">
-        <v>17594</v>
+        <v>25746</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>111.12</v>
+        <v>162.89</v>
       </c>
       <c r="B462" t="n">
-        <v>30134</v>
+        <v>27494</v>
       </c>
       <c r="C462" t="n">
-        <v>106.68</v>
+        <v>155.26</v>
       </c>
       <c r="D462" t="n">
-        <v>17238</v>
+        <v>16938</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>95.22</v>
+        <v>162.95</v>
       </c>
       <c r="B463" t="n">
-        <v>33380</v>
+        <v>29265</v>
       </c>
       <c r="C463" t="n">
-        <v>94.66</v>
+        <v>180</v>
       </c>
       <c r="D463" t="n">
-        <v>24429</v>
+        <v>28122</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>101.1</v>
+        <v>163.28</v>
       </c>
       <c r="B464" t="n">
-        <v>43268</v>
+        <v>29674</v>
       </c>
       <c r="C464" t="n">
-        <v>97.56999999999999</v>
+        <v>154.3</v>
       </c>
       <c r="D464" t="n">
-        <v>26047</v>
+        <v>19324</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>100.54</v>
+        <v>163.61</v>
       </c>
       <c r="B465" t="n">
-        <v>47387</v>
+        <v>30601</v>
       </c>
       <c r="C465" t="n">
-        <v>98.54000000000001</v>
+        <v>176.57</v>
       </c>
       <c r="D465" t="n">
-        <v>25920</v>
+        <v>15627</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>69.55</v>
+        <v>163.85</v>
       </c>
       <c r="B466" t="n">
-        <v>24470</v>
+        <v>27704</v>
       </c>
       <c r="C466" t="n">
-        <v>71.12</v>
+        <v>147.46</v>
       </c>
       <c r="D466" t="n">
-        <v>26846</v>
+        <v>26600</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>95.09999999999999</v>
+        <v>164</v>
       </c>
       <c r="B467" t="n">
-        <v>33930</v>
+        <v>26407</v>
       </c>
       <c r="C467" t="n">
-        <v>96.90000000000001</v>
+        <v>169.78</v>
       </c>
       <c r="D467" t="n">
-        <v>25256</v>
+        <v>15485</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>93.29000000000001</v>
+        <v>164.15</v>
       </c>
       <c r="B468" t="n">
-        <v>27050</v>
+        <v>27733</v>
       </c>
       <c r="C468" t="n">
-        <v>92.89</v>
+        <v>130.04</v>
       </c>
       <c r="D468" t="n">
-        <v>24807</v>
+        <v>14610</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>103.38</v>
+        <v>164.35</v>
       </c>
       <c r="B469" t="n">
-        <v>47908</v>
+        <v>28543</v>
       </c>
       <c r="C469" t="n">
-        <v>103.93</v>
+        <v>159.82</v>
       </c>
       <c r="D469" t="n">
-        <v>18693</v>
+        <v>20324</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>93.48</v>
+        <v>164.44</v>
       </c>
       <c r="B470" t="n">
-        <v>27772</v>
+        <v>29268</v>
       </c>
       <c r="C470" t="n">
-        <v>89.77</v>
+        <v>180</v>
       </c>
       <c r="D470" t="n">
-        <v>28336</v>
+        <v>16223</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>91.31</v>
+        <v>165.21</v>
       </c>
       <c r="B471" t="n">
-        <v>24868</v>
+        <v>27991</v>
       </c>
       <c r="C471" t="n">
-        <v>90.98</v>
+        <v>172.47</v>
       </c>
       <c r="D471" t="n">
-        <v>16261</v>
+        <v>18943</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>90.54000000000001</v>
+        <v>165.73</v>
       </c>
       <c r="B472" t="n">
-        <v>24771</v>
+        <v>25266</v>
       </c>
       <c r="C472" t="n">
-        <v>87.66</v>
+        <v>161.24</v>
       </c>
       <c r="D472" t="n">
-        <v>18344</v>
+        <v>26530</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>109.75</v>
+        <v>166.02</v>
       </c>
       <c r="B473" t="n">
-        <v>32140</v>
+        <v>24663</v>
       </c>
       <c r="C473" t="n">
-        <v>113.31</v>
+        <v>180</v>
       </c>
       <c r="D473" t="n">
-        <v>22228</v>
+        <v>26004</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>102.78</v>
+        <v>166.03</v>
       </c>
       <c r="B474" t="n">
-        <v>46520</v>
+        <v>27106</v>
       </c>
       <c r="C474" t="n">
-        <v>102</v>
+        <v>143.57</v>
       </c>
       <c r="D474" t="n">
-        <v>16659</v>
+        <v>19130</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>98.31</v>
+        <v>166.25</v>
       </c>
       <c r="B475" t="n">
-        <v>42414</v>
+        <v>27572</v>
       </c>
       <c r="C475" t="n">
-        <v>94.66</v>
+        <v>145.64</v>
       </c>
       <c r="D475" t="n">
-        <v>16296</v>
+        <v>10956</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>107.65</v>
+        <v>166.96</v>
       </c>
       <c r="B476" t="n">
-        <v>37255</v>
+        <v>25692</v>
       </c>
       <c r="C476" t="n">
-        <v>108.7</v>
+        <v>180</v>
       </c>
       <c r="D476" t="n">
-        <v>11957</v>
+        <v>14119</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>94.73</v>
+        <v>167.42</v>
       </c>
       <c r="B477" t="n">
-        <v>30841</v>
+        <v>23549</v>
       </c>
       <c r="C477" t="n">
-        <v>96.31</v>
+        <v>130.22</v>
       </c>
       <c r="D477" t="n">
-        <v>16547</v>
+        <v>13743</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>90.33</v>
+        <v>167.56</v>
       </c>
       <c r="B478" t="n">
-        <v>25592</v>
+        <v>25955</v>
       </c>
       <c r="C478" t="n">
-        <v>93.08</v>
+        <v>171.73</v>
       </c>
       <c r="D478" t="n">
-        <v>11250</v>
+        <v>27382</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>103.04</v>
+        <v>167.65</v>
       </c>
       <c r="B479" t="n">
-        <v>47579</v>
+        <v>24697</v>
       </c>
       <c r="C479" t="n">
-        <v>100.68</v>
+        <v>136.61</v>
       </c>
       <c r="D479" t="n">
-        <v>11442</v>
+        <v>23901</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>112.04</v>
+        <v>167.75</v>
       </c>
       <c r="B480" t="n">
-        <v>28321</v>
+        <v>24139</v>
       </c>
       <c r="C480" t="n">
-        <v>114.64</v>
+        <v>130.98</v>
       </c>
       <c r="D480" t="n">
-        <v>15790</v>
+        <v>25097</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>111.89</v>
+        <v>167.84</v>
       </c>
       <c r="B481" t="n">
-        <v>27830</v>
+        <v>26408</v>
       </c>
       <c r="C481" t="n">
-        <v>114.43</v>
+        <v>159.64</v>
       </c>
       <c r="D481" t="n">
-        <v>26341</v>
+        <v>19524</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>92.84</v>
+        <v>167.97</v>
       </c>
       <c r="B482" t="n">
-        <v>25585</v>
+        <v>24813</v>
       </c>
       <c r="C482" t="n">
-        <v>90.83</v>
+        <v>136.43</v>
       </c>
       <c r="D482" t="n">
-        <v>19862</v>
+        <v>25876</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>108.85</v>
+        <v>168.02</v>
       </c>
       <c r="B483" t="n">
-        <v>35382</v>
+        <v>25659</v>
       </c>
       <c r="C483" t="n">
-        <v>109.23</v>
+        <v>145.01</v>
       </c>
       <c r="D483" t="n">
-        <v>13007</v>
+        <v>12077</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>108.72</v>
+        <v>168.56</v>
       </c>
       <c r="B484" t="n">
-        <v>36130</v>
+        <v>21102</v>
       </c>
       <c r="C484" t="n">
-        <v>108.9</v>
+        <v>180</v>
       </c>
       <c r="D484" t="n">
-        <v>24930</v>
+        <v>19662</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>109.83</v>
+        <v>168.77</v>
       </c>
       <c r="B485" t="n">
-        <v>32835</v>
+        <v>23287</v>
       </c>
       <c r="C485" t="n">
-        <v>108.26</v>
+        <v>128.1</v>
       </c>
       <c r="D485" t="n">
-        <v>23056</v>
+        <v>20730</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>102.21</v>
+        <v>169.13</v>
       </c>
       <c r="B486" t="n">
-        <v>47366</v>
+        <v>22343</v>
       </c>
       <c r="C486" t="n">
-        <v>100.55</v>
+        <v>140.2</v>
       </c>
       <c r="D486" t="n">
-        <v>29141</v>
+        <v>23265</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>114.31</v>
+        <v>169.5</v>
       </c>
       <c r="B487" t="n">
-        <v>24455</v>
+        <v>22494</v>
       </c>
       <c r="C487" t="n">
-        <v>116.26</v>
+        <v>180</v>
       </c>
       <c r="D487" t="n">
-        <v>11655</v>
+        <v>26180</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>99.98999999999999</v>
+        <v>169.58</v>
       </c>
       <c r="B488" t="n">
-        <v>43813</v>
+        <v>21429</v>
       </c>
       <c r="C488" t="n">
-        <v>100.63</v>
+        <v>164.89</v>
       </c>
       <c r="D488" t="n">
-        <v>23554</v>
+        <v>24584</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>95.41</v>
+        <v>169.68</v>
       </c>
       <c r="B489" t="n">
-        <v>34291</v>
+        <v>22856</v>
       </c>
       <c r="C489" t="n">
-        <v>95.53</v>
+        <v>138.92</v>
       </c>
       <c r="D489" t="n">
-        <v>12806</v>
+        <v>12659</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>107.47</v>
+        <v>169.96</v>
       </c>
       <c r="B490" t="n">
-        <v>36785</v>
+        <v>22499</v>
       </c>
       <c r="C490" t="n">
-        <v>110.71</v>
+        <v>166.79</v>
       </c>
       <c r="D490" t="n">
-        <v>29451</v>
+        <v>13553</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>114.06</v>
+        <v>172.55</v>
       </c>
       <c r="B491" t="n">
-        <v>25413</v>
+        <v>20985</v>
       </c>
       <c r="C491" t="n">
-        <v>115.32</v>
+        <v>148.15</v>
       </c>
       <c r="D491" t="n">
-        <v>25347</v>
+        <v>27879</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>110.49</v>
+        <v>172.76</v>
       </c>
       <c r="B492" t="n">
-        <v>31038</v>
+        <v>23145</v>
       </c>
       <c r="C492" t="n">
-        <v>109.48</v>
+        <v>167.7</v>
       </c>
       <c r="D492" t="n">
-        <v>29310</v>
+        <v>10114</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>92.84999999999999</v>
+        <v>172.79</v>
       </c>
       <c r="B493" t="n">
-        <v>28027</v>
+        <v>20446</v>
       </c>
       <c r="C493" t="n">
-        <v>91.70999999999999</v>
+        <v>180</v>
       </c>
       <c r="D493" t="n">
-        <v>17520</v>
+        <v>11352</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>100.45</v>
+        <v>173.55</v>
       </c>
       <c r="B494" t="n">
-        <v>41348</v>
+        <v>18481</v>
       </c>
       <c r="C494" t="n">
-        <v>99.63</v>
+        <v>157.03</v>
       </c>
       <c r="D494" t="n">
-        <v>25331</v>
+        <v>29578</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>101.56</v>
+        <v>174.41</v>
       </c>
       <c r="B495" t="n">
-        <v>44618</v>
+        <v>20724</v>
       </c>
       <c r="C495" t="n">
-        <v>100.68</v>
+        <v>180</v>
       </c>
       <c r="D495" t="n">
-        <v>28296</v>
+        <v>12916</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>94.01000000000001</v>
+        <v>175.32</v>
       </c>
       <c r="B496" t="n">
-        <v>29849</v>
+        <v>18240</v>
       </c>
       <c r="C496" t="n">
-        <v>95.44</v>
+        <v>180</v>
       </c>
       <c r="D496" t="n">
-        <v>15018</v>
+        <v>21847</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>114.52</v>
+        <v>176.48</v>
       </c>
       <c r="B497" t="n">
-        <v>23058</v>
+        <v>18555</v>
       </c>
       <c r="C497" t="n">
-        <v>114.81</v>
+        <v>180</v>
       </c>
       <c r="D497" t="n">
-        <v>15968</v>
+        <v>11448</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>42.42</v>
+        <v>177.77</v>
       </c>
       <c r="B498" t="n">
-        <v>19209</v>
+        <v>18926</v>
       </c>
       <c r="C498" t="n">
-        <v>42.4</v>
+        <v>180</v>
       </c>
       <c r="D498" t="n">
-        <v>28009</v>
+        <v>12236</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>101.79</v>
+        <v>178.41</v>
       </c>
       <c r="B499" t="n">
-        <v>45950</v>
+        <v>17752</v>
       </c>
       <c r="C499" t="n">
-        <v>99.77</v>
+        <v>165.18</v>
       </c>
       <c r="D499" t="n">
-        <v>11798</v>
+        <v>22821</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>101.32</v>
+        <v>179.35</v>
       </c>
       <c r="B500" t="n">
-        <v>48374</v>
+        <v>20930</v>
       </c>
       <c r="C500" t="n">
-        <v>100.64</v>
+        <v>180</v>
       </c>
       <c r="D500" t="n">
-        <v>13205</v>
+        <v>19021</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>96.48999999999999</v>
+        <v>179.93</v>
       </c>
       <c r="B501" t="n">
-        <v>37137</v>
+        <v>18552</v>
       </c>
       <c r="C501" t="n">
-        <v>93.28</v>
+        <v>156.4</v>
       </c>
       <c r="D501" t="n">
-        <v>29221</v>
+        <v>29930</v>
       </c>
     </row>
   </sheetData>
